--- a/web/public/forms/chg-chongwal.xlsx
+++ b/web/public/forms/chg-chongwal.xlsx
@@ -8,9 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="설계변경 총괄표" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'설계변경 총괄표'!$A$1:$X$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$X$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,8 +20,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+  <numFmts count="6">
+    <numFmt numFmtId="164" formatCode="#,##0;[Red]-#,##0;&quot;&quot;"/>
+    <numFmt numFmtId="165" formatCode="yyyy&quot;년&quot; m&quot;월&quot; d&quot;일&quot;"/>
+    <numFmt numFmtId="166" formatCode="yyyy. m. d."/>
+    <numFmt numFmtId="167" formatCode="#,##0&quot;일&quot;;[Red]-#,##0&quot;일&quot;;&quot;&quot;"/>
+    <numFmt numFmtId="168" formatCode="0.000%;[Red]-0.000%;&quot;&quot;"/>
+    <numFmt numFmtId="169" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,32 +40,48 @@
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="000F203F"/>
-      <sz val="10.5"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00222222"/>
+      <color rgb="006B7280"/>
       <sz val="8.5"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="000F203F"/>
+      <color rgb="00111827"/>
       <sz val="19"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="000F203F"/>
+      <color rgb="001F2937"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00222222"/>
+      <color rgb="00000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F2937"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F2937"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -65,12 +90,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6F8FC"/>
+        <fgColor rgb="00F3F5F9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF3FB"/>
+        <fgColor rgb="00E8EEF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF4FC"/>
       </patternFill>
     </fill>
   </fills>
@@ -84,23 +114,23 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </left>
       <right style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </right>
       <top style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -109,32 +139,65 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -530,15 +593,15 @@
     <col width="3.6" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵   |   k-conmap.com   무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">← 이 1행을 지우고 쓰셔도 됩니다   </t>
+          <t xml:space="preserve">← 이 1행을 지우고 쓰셔도 됩니다  </t>
         </is>
       </c>
     </row>
@@ -562,7 +625,7 @@
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="n"/>
       <c r="H5" s="5" t="n"/>
       <c r="I5" s="5" t="n"/>
       <c r="J5" s="5" t="n"/>
@@ -592,7 +655,7 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="n"/>
       <c r="H6" s="5" t="n"/>
       <c r="I6" s="5" t="n"/>
       <c r="J6" s="5" t="n"/>
@@ -622,7 +685,7 @@
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr"/>
+      <c r="G7" s="7" t="n"/>
       <c r="H7" s="5" t="n"/>
       <c r="I7" s="5" t="n"/>
       <c r="J7" s="5" t="n"/>
@@ -652,7 +715,7 @@
       <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="inlineStr"/>
+      <c r="G8" s="8" t="n"/>
       <c r="H8" s="5" t="n"/>
       <c r="I8" s="5" t="n"/>
       <c r="J8" s="5" t="n"/>
@@ -673,20 +736,20 @@
     </row>
     <row r="9" ht="6" customHeight="1"/>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>차수</t>
         </is>
       </c>
       <c r="B10" s="5" t="n"/>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>변경일자</t>
         </is>
       </c>
       <c r="D10" s="5" t="n"/>
       <c r="E10" s="5" t="n"/>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>사  유</t>
         </is>
@@ -695,34 +758,34 @@
       <c r="H10" s="5" t="n"/>
       <c r="I10" s="5" t="n"/>
       <c r="J10" s="5" t="n"/>
-      <c r="K10" s="7" t="inlineStr">
+      <c r="K10" s="9" t="inlineStr">
         <is>
           <t>변경 전 금액</t>
         </is>
       </c>
       <c r="L10" s="5" t="n"/>
       <c r="M10" s="5" t="n"/>
-      <c r="N10" s="7" t="inlineStr">
+      <c r="N10" s="9" t="inlineStr">
         <is>
           <t>증감액</t>
         </is>
       </c>
       <c r="O10" s="5" t="n"/>
       <c r="P10" s="5" t="n"/>
-      <c r="Q10" s="7" t="inlineStr">
+      <c r="Q10" s="9" t="inlineStr">
         <is>
           <t>변경 후 금액</t>
         </is>
       </c>
       <c r="R10" s="5" t="n"/>
       <c r="S10" s="5" t="n"/>
-      <c r="T10" s="7" t="inlineStr">
+      <c r="T10" s="9" t="inlineStr">
         <is>
           <t>공기증감(일)</t>
         </is>
       </c>
       <c r="U10" s="5" t="n"/>
-      <c r="V10" s="7" t="inlineStr">
+      <c r="V10" s="9" t="inlineStr">
         <is>
           <t>변경 후 준공기한</t>
         </is>
@@ -731,320 +794,428 @@
       <c r="X10" s="5" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="8" t="inlineStr"/>
+      <c r="A11" s="10" t="n"/>
       <c r="B11" s="5" t="n"/>
-      <c r="C11" s="8" t="inlineStr"/>
+      <c r="C11" s="11" t="n"/>
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>
-      <c r="F11" s="8" t="inlineStr"/>
+      <c r="F11" s="10" t="n"/>
       <c r="G11" s="5" t="n"/>
       <c r="H11" s="5" t="n"/>
       <c r="I11" s="5" t="n"/>
       <c r="J11" s="5" t="n"/>
-      <c r="K11" s="8" t="inlineStr"/>
+      <c r="K11" s="12">
+        <f>IF(N11="","",N(G7))</f>
+        <v/>
+      </c>
       <c r="L11" s="5" t="n"/>
       <c r="M11" s="5" t="n"/>
-      <c r="N11" s="8" t="inlineStr"/>
+      <c r="N11" s="7" t="n"/>
       <c r="O11" s="5" t="n"/>
       <c r="P11" s="5" t="n"/>
-      <c r="Q11" s="8" t="inlineStr"/>
+      <c r="Q11" s="12">
+        <f>IF(N11="","",K11+N11)</f>
+        <v/>
+      </c>
       <c r="R11" s="5" t="n"/>
       <c r="S11" s="5" t="n"/>
-      <c r="T11" s="8" t="inlineStr"/>
+      <c r="T11" s="13" t="n"/>
       <c r="U11" s="5" t="n"/>
-      <c r="V11" s="8" t="inlineStr"/>
+      <c r="V11" s="14">
+        <f>IF(AND(N11="",T11=""),"",G8+N(T11))</f>
+        <v/>
+      </c>
       <c r="W11" s="5" t="n"/>
       <c r="X11" s="5" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="8" t="inlineStr"/>
+      <c r="A12" s="10" t="n"/>
       <c r="B12" s="5" t="n"/>
-      <c r="C12" s="8" t="inlineStr"/>
+      <c r="C12" s="11" t="n"/>
       <c r="D12" s="5" t="n"/>
       <c r="E12" s="5" t="n"/>
-      <c r="F12" s="8" t="inlineStr"/>
+      <c r="F12" s="10" t="n"/>
       <c r="G12" s="5" t="n"/>
       <c r="H12" s="5" t="n"/>
       <c r="I12" s="5" t="n"/>
       <c r="J12" s="5" t="n"/>
-      <c r="K12" s="8" t="inlineStr"/>
+      <c r="K12" s="12">
+        <f>IF(N12="","",N(G7)+SUM(N11:N11))</f>
+        <v/>
+      </c>
       <c r="L12" s="5" t="n"/>
       <c r="M12" s="5" t="n"/>
-      <c r="N12" s="8" t="inlineStr"/>
+      <c r="N12" s="7" t="n"/>
       <c r="O12" s="5" t="n"/>
       <c r="P12" s="5" t="n"/>
-      <c r="Q12" s="8" t="inlineStr"/>
+      <c r="Q12" s="12">
+        <f>IF(N12="","",K12+N12)</f>
+        <v/>
+      </c>
       <c r="R12" s="5" t="n"/>
       <c r="S12" s="5" t="n"/>
-      <c r="T12" s="8" t="inlineStr"/>
+      <c r="T12" s="13" t="n"/>
       <c r="U12" s="5" t="n"/>
-      <c r="V12" s="8" t="inlineStr"/>
+      <c r="V12" s="14">
+        <f>IF(AND(N12="",T12=""),"",G8+SUM(T11:T12))</f>
+        <v/>
+      </c>
       <c r="W12" s="5" t="n"/>
       <c r="X12" s="5" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="8" t="inlineStr"/>
+      <c r="A13" s="10" t="n"/>
       <c r="B13" s="5" t="n"/>
-      <c r="C13" s="8" t="inlineStr"/>
+      <c r="C13" s="11" t="n"/>
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
-      <c r="F13" s="8" t="inlineStr"/>
+      <c r="F13" s="10" t="n"/>
       <c r="G13" s="5" t="n"/>
       <c r="H13" s="5" t="n"/>
       <c r="I13" s="5" t="n"/>
       <c r="J13" s="5" t="n"/>
-      <c r="K13" s="8" t="inlineStr"/>
+      <c r="K13" s="12">
+        <f>IF(N13="","",N(G7)+SUM(N11:N12))</f>
+        <v/>
+      </c>
       <c r="L13" s="5" t="n"/>
       <c r="M13" s="5" t="n"/>
-      <c r="N13" s="8" t="inlineStr"/>
+      <c r="N13" s="7" t="n"/>
       <c r="O13" s="5" t="n"/>
       <c r="P13" s="5" t="n"/>
-      <c r="Q13" s="8" t="inlineStr"/>
+      <c r="Q13" s="12">
+        <f>IF(N13="","",K13+N13)</f>
+        <v/>
+      </c>
       <c r="R13" s="5" t="n"/>
       <c r="S13" s="5" t="n"/>
-      <c r="T13" s="8" t="inlineStr"/>
+      <c r="T13" s="13" t="n"/>
       <c r="U13" s="5" t="n"/>
-      <c r="V13" s="8" t="inlineStr"/>
+      <c r="V13" s="14">
+        <f>IF(AND(N13="",T13=""),"",G8+SUM(T11:T13))</f>
+        <v/>
+      </c>
       <c r="W13" s="5" t="n"/>
       <c r="X13" s="5" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="8" t="inlineStr"/>
+      <c r="A14" s="10" t="n"/>
       <c r="B14" s="5" t="n"/>
-      <c r="C14" s="8" t="inlineStr"/>
+      <c r="C14" s="11" t="n"/>
       <c r="D14" s="5" t="n"/>
       <c r="E14" s="5" t="n"/>
-      <c r="F14" s="8" t="inlineStr"/>
+      <c r="F14" s="10" t="n"/>
       <c r="G14" s="5" t="n"/>
       <c r="H14" s="5" t="n"/>
       <c r="I14" s="5" t="n"/>
       <c r="J14" s="5" t="n"/>
-      <c r="K14" s="8" t="inlineStr"/>
+      <c r="K14" s="12">
+        <f>IF(N14="","",N(G7)+SUM(N11:N13))</f>
+        <v/>
+      </c>
       <c r="L14" s="5" t="n"/>
       <c r="M14" s="5" t="n"/>
-      <c r="N14" s="8" t="inlineStr"/>
+      <c r="N14" s="7" t="n"/>
       <c r="O14" s="5" t="n"/>
       <c r="P14" s="5" t="n"/>
-      <c r="Q14" s="8" t="inlineStr"/>
+      <c r="Q14" s="12">
+        <f>IF(N14="","",K14+N14)</f>
+        <v/>
+      </c>
       <c r="R14" s="5" t="n"/>
       <c r="S14" s="5" t="n"/>
-      <c r="T14" s="8" t="inlineStr"/>
+      <c r="T14" s="13" t="n"/>
       <c r="U14" s="5" t="n"/>
-      <c r="V14" s="8" t="inlineStr"/>
+      <c r="V14" s="14">
+        <f>IF(AND(N14="",T14=""),"",G8+SUM(T11:T14))</f>
+        <v/>
+      </c>
       <c r="W14" s="5" t="n"/>
       <c r="X14" s="5" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="8" t="inlineStr"/>
+      <c r="A15" s="10" t="n"/>
       <c r="B15" s="5" t="n"/>
-      <c r="C15" s="8" t="inlineStr"/>
+      <c r="C15" s="11" t="n"/>
       <c r="D15" s="5" t="n"/>
       <c r="E15" s="5" t="n"/>
-      <c r="F15" s="8" t="inlineStr"/>
+      <c r="F15" s="10" t="n"/>
       <c r="G15" s="5" t="n"/>
       <c r="H15" s="5" t="n"/>
       <c r="I15" s="5" t="n"/>
       <c r="J15" s="5" t="n"/>
-      <c r="K15" s="8" t="inlineStr"/>
+      <c r="K15" s="12">
+        <f>IF(N15="","",N(G7)+SUM(N11:N14))</f>
+        <v/>
+      </c>
       <c r="L15" s="5" t="n"/>
       <c r="M15" s="5" t="n"/>
-      <c r="N15" s="8" t="inlineStr"/>
+      <c r="N15" s="7" t="n"/>
       <c r="O15" s="5" t="n"/>
       <c r="P15" s="5" t="n"/>
-      <c r="Q15" s="8" t="inlineStr"/>
+      <c r="Q15" s="12">
+        <f>IF(N15="","",K15+N15)</f>
+        <v/>
+      </c>
       <c r="R15" s="5" t="n"/>
       <c r="S15" s="5" t="n"/>
-      <c r="T15" s="8" t="inlineStr"/>
+      <c r="T15" s="13" t="n"/>
       <c r="U15" s="5" t="n"/>
-      <c r="V15" s="8" t="inlineStr"/>
+      <c r="V15" s="14">
+        <f>IF(AND(N15="",T15=""),"",G8+SUM(T11:T15))</f>
+        <v/>
+      </c>
       <c r="W15" s="5" t="n"/>
       <c r="X15" s="5" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="8" t="inlineStr"/>
+      <c r="A16" s="10" t="n"/>
       <c r="B16" s="5" t="n"/>
-      <c r="C16" s="8" t="inlineStr"/>
+      <c r="C16" s="11" t="n"/>
       <c r="D16" s="5" t="n"/>
       <c r="E16" s="5" t="n"/>
-      <c r="F16" s="8" t="inlineStr"/>
+      <c r="F16" s="10" t="n"/>
       <c r="G16" s="5" t="n"/>
       <c r="H16" s="5" t="n"/>
       <c r="I16" s="5" t="n"/>
       <c r="J16" s="5" t="n"/>
-      <c r="K16" s="8" t="inlineStr"/>
+      <c r="K16" s="12">
+        <f>IF(N16="","",N(G7)+SUM(N11:N15))</f>
+        <v/>
+      </c>
       <c r="L16" s="5" t="n"/>
       <c r="M16" s="5" t="n"/>
-      <c r="N16" s="8" t="inlineStr"/>
+      <c r="N16" s="7" t="n"/>
       <c r="O16" s="5" t="n"/>
       <c r="P16" s="5" t="n"/>
-      <c r="Q16" s="8" t="inlineStr"/>
+      <c r="Q16" s="12">
+        <f>IF(N16="","",K16+N16)</f>
+        <v/>
+      </c>
       <c r="R16" s="5" t="n"/>
       <c r="S16" s="5" t="n"/>
-      <c r="T16" s="8" t="inlineStr"/>
+      <c r="T16" s="13" t="n"/>
       <c r="U16" s="5" t="n"/>
-      <c r="V16" s="8" t="inlineStr"/>
+      <c r="V16" s="14">
+        <f>IF(AND(N16="",T16=""),"",G8+SUM(T11:T16))</f>
+        <v/>
+      </c>
       <c r="W16" s="5" t="n"/>
       <c r="X16" s="5" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="8" t="inlineStr"/>
+      <c r="A17" s="10" t="n"/>
       <c r="B17" s="5" t="n"/>
-      <c r="C17" s="8" t="inlineStr"/>
+      <c r="C17" s="11" t="n"/>
       <c r="D17" s="5" t="n"/>
       <c r="E17" s="5" t="n"/>
-      <c r="F17" s="8" t="inlineStr"/>
+      <c r="F17" s="10" t="n"/>
       <c r="G17" s="5" t="n"/>
       <c r="H17" s="5" t="n"/>
       <c r="I17" s="5" t="n"/>
       <c r="J17" s="5" t="n"/>
-      <c r="K17" s="8" t="inlineStr"/>
+      <c r="K17" s="12">
+        <f>IF(N17="","",N(G7)+SUM(N11:N16))</f>
+        <v/>
+      </c>
       <c r="L17" s="5" t="n"/>
       <c r="M17" s="5" t="n"/>
-      <c r="N17" s="8" t="inlineStr"/>
+      <c r="N17" s="7" t="n"/>
       <c r="O17" s="5" t="n"/>
       <c r="P17" s="5" t="n"/>
-      <c r="Q17" s="8" t="inlineStr"/>
+      <c r="Q17" s="12">
+        <f>IF(N17="","",K17+N17)</f>
+        <v/>
+      </c>
       <c r="R17" s="5" t="n"/>
       <c r="S17" s="5" t="n"/>
-      <c r="T17" s="8" t="inlineStr"/>
+      <c r="T17" s="13" t="n"/>
       <c r="U17" s="5" t="n"/>
-      <c r="V17" s="8" t="inlineStr"/>
+      <c r="V17" s="14">
+        <f>IF(AND(N17="",T17=""),"",G8+SUM(T11:T17))</f>
+        <v/>
+      </c>
       <c r="W17" s="5" t="n"/>
       <c r="X17" s="5" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="8" t="inlineStr"/>
+      <c r="A18" s="10" t="n"/>
       <c r="B18" s="5" t="n"/>
-      <c r="C18" s="8" t="inlineStr"/>
+      <c r="C18" s="11" t="n"/>
       <c r="D18" s="5" t="n"/>
       <c r="E18" s="5" t="n"/>
-      <c r="F18" s="8" t="inlineStr"/>
+      <c r="F18" s="10" t="n"/>
       <c r="G18" s="5" t="n"/>
       <c r="H18" s="5" t="n"/>
       <c r="I18" s="5" t="n"/>
       <c r="J18" s="5" t="n"/>
-      <c r="K18" s="8" t="inlineStr"/>
+      <c r="K18" s="12">
+        <f>IF(N18="","",N(G7)+SUM(N11:N17))</f>
+        <v/>
+      </c>
       <c r="L18" s="5" t="n"/>
       <c r="M18" s="5" t="n"/>
-      <c r="N18" s="8" t="inlineStr"/>
+      <c r="N18" s="7" t="n"/>
       <c r="O18" s="5" t="n"/>
       <c r="P18" s="5" t="n"/>
-      <c r="Q18" s="8" t="inlineStr"/>
+      <c r="Q18" s="12">
+        <f>IF(N18="","",K18+N18)</f>
+        <v/>
+      </c>
       <c r="R18" s="5" t="n"/>
       <c r="S18" s="5" t="n"/>
-      <c r="T18" s="8" t="inlineStr"/>
+      <c r="T18" s="13" t="n"/>
       <c r="U18" s="5" t="n"/>
-      <c r="V18" s="8" t="inlineStr"/>
+      <c r="V18" s="14">
+        <f>IF(AND(N18="",T18=""),"",G8+SUM(T11:T18))</f>
+        <v/>
+      </c>
       <c r="W18" s="5" t="n"/>
       <c r="X18" s="5" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="8" t="inlineStr"/>
+      <c r="A19" s="10" t="n"/>
       <c r="B19" s="5" t="n"/>
-      <c r="C19" s="8" t="inlineStr"/>
+      <c r="C19" s="11" t="n"/>
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="n"/>
-      <c r="F19" s="8" t="inlineStr"/>
+      <c r="F19" s="10" t="n"/>
       <c r="G19" s="5" t="n"/>
       <c r="H19" s="5" t="n"/>
       <c r="I19" s="5" t="n"/>
       <c r="J19" s="5" t="n"/>
-      <c r="K19" s="8" t="inlineStr"/>
+      <c r="K19" s="12">
+        <f>IF(N19="","",N(G7)+SUM(N11:N18))</f>
+        <v/>
+      </c>
       <c r="L19" s="5" t="n"/>
       <c r="M19" s="5" t="n"/>
-      <c r="N19" s="8" t="inlineStr"/>
+      <c r="N19" s="7" t="n"/>
       <c r="O19" s="5" t="n"/>
       <c r="P19" s="5" t="n"/>
-      <c r="Q19" s="8" t="inlineStr"/>
+      <c r="Q19" s="12">
+        <f>IF(N19="","",K19+N19)</f>
+        <v/>
+      </c>
       <c r="R19" s="5" t="n"/>
       <c r="S19" s="5" t="n"/>
-      <c r="T19" s="8" t="inlineStr"/>
+      <c r="T19" s="13" t="n"/>
       <c r="U19" s="5" t="n"/>
-      <c r="V19" s="8" t="inlineStr"/>
+      <c r="V19" s="14">
+        <f>IF(AND(N19="",T19=""),"",G8+SUM(T11:T19))</f>
+        <v/>
+      </c>
       <c r="W19" s="5" t="n"/>
       <c r="X19" s="5" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="8" t="inlineStr"/>
+      <c r="A20" s="10" t="n"/>
       <c r="B20" s="5" t="n"/>
-      <c r="C20" s="8" t="inlineStr"/>
+      <c r="C20" s="11" t="n"/>
       <c r="D20" s="5" t="n"/>
       <c r="E20" s="5" t="n"/>
-      <c r="F20" s="8" t="inlineStr"/>
+      <c r="F20" s="10" t="n"/>
       <c r="G20" s="5" t="n"/>
       <c r="H20" s="5" t="n"/>
       <c r="I20" s="5" t="n"/>
       <c r="J20" s="5" t="n"/>
-      <c r="K20" s="8" t="inlineStr"/>
+      <c r="K20" s="12">
+        <f>IF(N20="","",N(G7)+SUM(N11:N19))</f>
+        <v/>
+      </c>
       <c r="L20" s="5" t="n"/>
       <c r="M20" s="5" t="n"/>
-      <c r="N20" s="8" t="inlineStr"/>
+      <c r="N20" s="7" t="n"/>
       <c r="O20" s="5" t="n"/>
       <c r="P20" s="5" t="n"/>
-      <c r="Q20" s="8" t="inlineStr"/>
+      <c r="Q20" s="12">
+        <f>IF(N20="","",K20+N20)</f>
+        <v/>
+      </c>
       <c r="R20" s="5" t="n"/>
       <c r="S20" s="5" t="n"/>
-      <c r="T20" s="8" t="inlineStr"/>
+      <c r="T20" s="13" t="n"/>
       <c r="U20" s="5" t="n"/>
-      <c r="V20" s="8" t="inlineStr"/>
+      <c r="V20" s="14">
+        <f>IF(AND(N20="",T20=""),"",G8+SUM(T11:T20))</f>
+        <v/>
+      </c>
       <c r="W20" s="5" t="n"/>
       <c r="X20" s="5" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="8" t="inlineStr"/>
+      <c r="A21" s="10" t="n"/>
       <c r="B21" s="5" t="n"/>
-      <c r="C21" s="8" t="inlineStr"/>
+      <c r="C21" s="11" t="n"/>
       <c r="D21" s="5" t="n"/>
       <c r="E21" s="5" t="n"/>
-      <c r="F21" s="8" t="inlineStr"/>
+      <c r="F21" s="10" t="n"/>
       <c r="G21" s="5" t="n"/>
       <c r="H21" s="5" t="n"/>
       <c r="I21" s="5" t="n"/>
       <c r="J21" s="5" t="n"/>
-      <c r="K21" s="8" t="inlineStr"/>
+      <c r="K21" s="12">
+        <f>IF(N21="","",N(G7)+SUM(N11:N20))</f>
+        <v/>
+      </c>
       <c r="L21" s="5" t="n"/>
       <c r="M21" s="5" t="n"/>
-      <c r="N21" s="8" t="inlineStr"/>
+      <c r="N21" s="7" t="n"/>
       <c r="O21" s="5" t="n"/>
       <c r="P21" s="5" t="n"/>
-      <c r="Q21" s="8" t="inlineStr"/>
+      <c r="Q21" s="12">
+        <f>IF(N21="","",K21+N21)</f>
+        <v/>
+      </c>
       <c r="R21" s="5" t="n"/>
       <c r="S21" s="5" t="n"/>
-      <c r="T21" s="8" t="inlineStr"/>
+      <c r="T21" s="13" t="n"/>
       <c r="U21" s="5" t="n"/>
-      <c r="V21" s="8" t="inlineStr"/>
+      <c r="V21" s="14">
+        <f>IF(AND(N21="",T21=""),"",G8+SUM(T11:T21))</f>
+        <v/>
+      </c>
       <c r="W21" s="5" t="n"/>
       <c r="X21" s="5" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="8" t="inlineStr"/>
+      <c r="A22" s="10" t="n"/>
       <c r="B22" s="5" t="n"/>
-      <c r="C22" s="8" t="inlineStr"/>
+      <c r="C22" s="11" t="n"/>
       <c r="D22" s="5" t="n"/>
       <c r="E22" s="5" t="n"/>
-      <c r="F22" s="8" t="inlineStr"/>
+      <c r="F22" s="10" t="n"/>
       <c r="G22" s="5" t="n"/>
       <c r="H22" s="5" t="n"/>
       <c r="I22" s="5" t="n"/>
       <c r="J22" s="5" t="n"/>
-      <c r="K22" s="8" t="inlineStr"/>
+      <c r="K22" s="12">
+        <f>IF(N22="","",N(G7)+SUM(N11:N21))</f>
+        <v/>
+      </c>
       <c r="L22" s="5" t="n"/>
       <c r="M22" s="5" t="n"/>
-      <c r="N22" s="8" t="inlineStr"/>
+      <c r="N22" s="7" t="n"/>
       <c r="O22" s="5" t="n"/>
       <c r="P22" s="5" t="n"/>
-      <c r="Q22" s="8" t="inlineStr"/>
+      <c r="Q22" s="12">
+        <f>IF(N22="","",K22+N22)</f>
+        <v/>
+      </c>
       <c r="R22" s="5" t="n"/>
       <c r="S22" s="5" t="n"/>
-      <c r="T22" s="8" t="inlineStr"/>
+      <c r="T22" s="13" t="n"/>
       <c r="U22" s="5" t="n"/>
-      <c r="V22" s="8" t="inlineStr"/>
+      <c r="V22" s="14">
+        <f>IF(AND(N22="",T22=""),"",G8+SUM(T11:T22))</f>
+        <v/>
+      </c>
       <c r="W22" s="5" t="n"/>
       <c r="X22" s="5" t="n"/>
     </row>
     <row r="23" ht="6" customHeight="1"/>
     <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>※ 사유는 설계변경 / 물가변동 / 공기연장 으로 나누어 적습니다 — 근거 법령이 다릅니다.</t>
         </is>
@@ -1062,7 +1233,10 @@
       <c r="D26" s="5" t="n"/>
       <c r="E26" s="5" t="n"/>
       <c r="F26" s="5" t="n"/>
-      <c r="G26" s="6" t="inlineStr"/>
+      <c r="G26" s="12">
+        <f>SUMIF(N11:N22,"&gt;0")</f>
+        <v/>
+      </c>
       <c r="H26" s="5" t="n"/>
       <c r="I26" s="5" t="n"/>
       <c r="J26" s="5" t="n"/>
@@ -1092,7 +1266,10 @@
       <c r="D27" s="5" t="n"/>
       <c r="E27" s="5" t="n"/>
       <c r="F27" s="5" t="n"/>
-      <c r="G27" s="6" t="inlineStr"/>
+      <c r="G27" s="12">
+        <f>SUMIF(N11:N22,"&lt;0")</f>
+        <v/>
+      </c>
       <c r="H27" s="5" t="n"/>
       <c r="I27" s="5" t="n"/>
       <c r="J27" s="5" t="n"/>
@@ -1122,7 +1299,10 @@
       <c r="D28" s="5" t="n"/>
       <c r="E28" s="5" t="n"/>
       <c r="F28" s="5" t="n"/>
-      <c r="G28" s="6" t="inlineStr"/>
+      <c r="G28" s="12">
+        <f>N(G7)+SUM(N11:N22)</f>
+        <v/>
+      </c>
       <c r="H28" s="5" t="n"/>
       <c r="I28" s="5" t="n"/>
       <c r="J28" s="5" t="n"/>
@@ -1152,7 +1332,10 @@
       <c r="D29" s="5" t="n"/>
       <c r="E29" s="5" t="n"/>
       <c r="F29" s="5" t="n"/>
-      <c r="G29" s="6" t="inlineStr"/>
+      <c r="G29" s="16">
+        <f>IF(N(G7)=0,"",SUM(N11:N22)/G7)</f>
+        <v/>
+      </c>
       <c r="H29" s="5" t="n"/>
       <c r="I29" s="5" t="n"/>
       <c r="J29" s="5" t="n"/>
@@ -1174,62 +1357,74 @@
     <row r="30" ht="6" customHeight="1"/>
     <row r="31" ht="10" customHeight="1"/>
     <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>년        월        일</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="K33" s="11" t="inlineStr">
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          년        월        일</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="18" t="inlineStr"/>
+      <c r="K33" s="19" t="inlineStr">
         <is>
           <t>현장대리인</t>
         </is>
       </c>
-      <c r="S33" s="10" t="inlineStr">
+      <c r="Q33" s="20" t="n"/>
+      <c r="U33" s="21" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="K34" s="11" t="inlineStr">
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="18" t="inlineStr"/>
+      <c r="K34" s="19" t="inlineStr">
         <is>
           <t>감독</t>
         </is>
       </c>
-      <c r="S34" s="10" t="inlineStr">
+      <c r="Q34" s="20" t="n"/>
+      <c r="U34" s="21" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="K35" s="11" t="inlineStr">
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="18" t="inlineStr"/>
+      <c r="K35" s="19" t="inlineStr">
         <is>
           <t>발주기관</t>
         </is>
       </c>
-      <c r="S35" s="10" t="inlineStr">
+      <c r="Q35" s="20" t="n"/>
+      <c r="U35" s="21" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
         </is>
       </c>
     </row>
     <row r="36" ht="6" customHeight="1"/>
-    <row r="39">
-      <c r="A39" s="12" t="inlineStr">
-        <is>
-          <t>발주기관이 정한 서식이 있으면 그 서식을 사용하세요. 이 줄과 1행은 인쇄 전에 지우셔도 됩니다.</t>
+    <row r="38" ht="34" customHeight="1">
+      <c r="A38" s="22" t="inlineStr">
+        <is>
+          <t>노란 칸 = 요율·기준값(발주기관 기준으로 고쳐 씀) · 옅은 하늘색 칸 = 자동 계산(지우지 마세요) · 뒤 시트에 «작성 예시» 가 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="19.5" customHeight="1">
+      <c r="A39" s="22" t="inlineStr">
+        <is>
+          <t>발주기관이 정한 서식이 있으면 그 서식을 쓰세요. 이 줄과 1행은 지워도 됩니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="132">
+  <mergeCells count="139">
     <mergeCell ref="V10:X10"/>
     <mergeCell ref="Q14:S14"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="K34:R34"/>
     <mergeCell ref="F10:J10"/>
     <mergeCell ref="F19:J19"/>
     <mergeCell ref="N17:P17"/>
@@ -1238,6 +1433,7 @@
     <mergeCell ref="Q15:S15"/>
     <mergeCell ref="N19:P19"/>
     <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A34:J34"/>
     <mergeCell ref="F18:J18"/>
     <mergeCell ref="K17:M17"/>
     <mergeCell ref="A32:X32"/>
@@ -1247,17 +1443,22 @@
     <mergeCell ref="V22:X22"/>
     <mergeCell ref="K10:M10"/>
     <mergeCell ref="G29:X29"/>
+    <mergeCell ref="A38:X38"/>
     <mergeCell ref="C18:E18"/>
     <mergeCell ref="V12:X12"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="V21:X21"/>
     <mergeCell ref="K16:M16"/>
     <mergeCell ref="A22:B22"/>
+    <mergeCell ref="K33:P33"/>
     <mergeCell ref="V14:X14"/>
+    <mergeCell ref="Q35:T35"/>
     <mergeCell ref="A24:X24"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="V13:X13"/>
+    <mergeCell ref="Q34:T34"/>
     <mergeCell ref="K20:M20"/>
+    <mergeCell ref="K35:P35"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="K11:M11"/>
     <mergeCell ref="A7:F7"/>
@@ -1268,11 +1469,8 @@
     <mergeCell ref="N18:P18"/>
     <mergeCell ref="C22:E22"/>
     <mergeCell ref="A27:F27"/>
-    <mergeCell ref="K33:R33"/>
     <mergeCell ref="K12:M12"/>
     <mergeCell ref="C12:E12"/>
-    <mergeCell ref="S34:X34"/>
-    <mergeCell ref="K35:R35"/>
     <mergeCell ref="F21:J21"/>
     <mergeCell ref="T10:U10"/>
     <mergeCell ref="Q22:S22"/>
@@ -1299,6 +1497,7 @@
     <mergeCell ref="N21:P21"/>
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="C16:E16"/>
+    <mergeCell ref="U33:X33"/>
     <mergeCell ref="F11:J11"/>
     <mergeCell ref="T15:U15"/>
     <mergeCell ref="Q10:S10"/>
@@ -1308,12 +1507,10 @@
     <mergeCell ref="C11:E11"/>
     <mergeCell ref="F15:J15"/>
     <mergeCell ref="F12:J12"/>
-    <mergeCell ref="S33:X33"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="Q17:S17"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="V16:X16"/>
-    <mergeCell ref="S35:X35"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="K13:M13"/>
     <mergeCell ref="A14:B14"/>
@@ -1328,26 +1525,32 @@
     <mergeCell ref="T19:U19"/>
     <mergeCell ref="G27:X27"/>
     <mergeCell ref="K21:M21"/>
+    <mergeCell ref="A33:J33"/>
     <mergeCell ref="V19:X19"/>
     <mergeCell ref="F16:J16"/>
     <mergeCell ref="T20:U20"/>
     <mergeCell ref="T14:U14"/>
     <mergeCell ref="G28:X28"/>
+    <mergeCell ref="A35:J35"/>
     <mergeCell ref="G6:X6"/>
     <mergeCell ref="V11:X11"/>
     <mergeCell ref="A16:B16"/>
+    <mergeCell ref="U35:X35"/>
     <mergeCell ref="F20:J20"/>
     <mergeCell ref="N13:P13"/>
     <mergeCell ref="G5:X5"/>
     <mergeCell ref="C17:E17"/>
+    <mergeCell ref="U34:X34"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="T21:U21"/>
     <mergeCell ref="N15:P15"/>
     <mergeCell ref="Q11:S11"/>
+    <mergeCell ref="Q33:T33"/>
     <mergeCell ref="K19:M19"/>
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="F13:J13"/>
     <mergeCell ref="T13:U13"/>
+    <mergeCell ref="K34:P34"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="T16:U16"/>
     <mergeCell ref="N16:P16"/>
@@ -1359,7 +1562,1075 @@
     <mergeCell ref="G8:X8"/>
     <mergeCell ref="Q20:S20"/>
   </mergeCells>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00F59E0B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:X38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3.6" customWidth="1" min="1" max="1"/>
+    <col width="3.6" customWidth="1" min="2" max="2"/>
+    <col width="3.6" customWidth="1" min="3" max="3"/>
+    <col width="3.6" customWidth="1" min="4" max="4"/>
+    <col width="3.6" customWidth="1" min="5" max="5"/>
+    <col width="3.6" customWidth="1" min="6" max="6"/>
+    <col width="3.6" customWidth="1" min="7" max="7"/>
+    <col width="3.6" customWidth="1" min="8" max="8"/>
+    <col width="3.6" customWidth="1" min="9" max="9"/>
+    <col width="3.6" customWidth="1" min="10" max="10"/>
+    <col width="3.6" customWidth="1" min="11" max="11"/>
+    <col width="3.6" customWidth="1" min="12" max="12"/>
+    <col width="3.6" customWidth="1" min="13" max="13"/>
+    <col width="3.6" customWidth="1" min="14" max="14"/>
+    <col width="3.6" customWidth="1" min="15" max="15"/>
+    <col width="3.6" customWidth="1" min="16" max="16"/>
+    <col width="3.6" customWidth="1" min="17" max="17"/>
+    <col width="3.6" customWidth="1" min="18" max="18"/>
+    <col width="3.6" customWidth="1" min="19" max="19"/>
+    <col width="3.6" customWidth="1" min="20" max="20"/>
+    <col width="3.6" customWidth="1" min="21" max="21"/>
+    <col width="3.6" customWidth="1" min="22" max="22"/>
+    <col width="3.6" customWidth="1" min="23" max="23"/>
+    <col width="3.6" customWidth="1" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+        </is>
+      </c>
+      <c r="M1" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="6" customHeight="1"/>
+    <row r="3" ht="38" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>설 계 변 경 총 괄 표</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="10" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  공 사 명</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>가나지구 배수로 정비공사</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
+      <c r="Q5" s="5" t="n"/>
+      <c r="R5" s="5" t="n"/>
+      <c r="S5" s="5" t="n"/>
+      <c r="T5" s="5" t="n"/>
+      <c r="U5" s="5" t="n"/>
+      <c r="V5" s="5" t="n"/>
+      <c r="W5" s="5" t="n"/>
+      <c r="X5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  계약번호</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>제2026-0312호</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
+      <c r="Q6" s="5" t="n"/>
+      <c r="R6" s="5" t="n"/>
+      <c r="S6" s="5" t="n"/>
+      <c r="T6" s="5" t="n"/>
+      <c r="U6" s="5" t="n"/>
+      <c r="V6" s="5" t="n"/>
+      <c r="W6" s="5" t="n"/>
+      <c r="X6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  최초 계약금액</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="7" t="n">
+        <v>963241000</v>
+      </c>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+      <c r="P7" s="5" t="n"/>
+      <c r="Q7" s="5" t="n"/>
+      <c r="R7" s="5" t="n"/>
+      <c r="S7" s="5" t="n"/>
+      <c r="T7" s="5" t="n"/>
+      <c r="U7" s="5" t="n"/>
+      <c r="V7" s="5" t="n"/>
+      <c r="W7" s="5" t="n"/>
+      <c r="X7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  최초 준공기한</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="8" t="n">
+        <v>46387</v>
+      </c>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
+      <c r="Q8" s="5" t="n"/>
+      <c r="R8" s="5" t="n"/>
+      <c r="S8" s="5" t="n"/>
+      <c r="T8" s="5" t="n"/>
+      <c r="U8" s="5" t="n"/>
+      <c r="V8" s="5" t="n"/>
+      <c r="W8" s="5" t="n"/>
+      <c r="X8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="6" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>차수</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>변경일자</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>사  유</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>변경 전 금액</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="9" t="inlineStr">
+        <is>
+          <t>증감액</t>
+        </is>
+      </c>
+      <c r="O10" s="5" t="n"/>
+      <c r="P10" s="5" t="n"/>
+      <c r="Q10" s="9" t="inlineStr">
+        <is>
+          <t>변경 후 금액</t>
+        </is>
+      </c>
+      <c r="R10" s="5" t="n"/>
+      <c r="S10" s="5" t="n"/>
+      <c r="T10" s="9" t="inlineStr">
+        <is>
+          <t>공기증감(일)</t>
+        </is>
+      </c>
+      <c r="U10" s="5" t="n"/>
+      <c r="V10" s="9" t="inlineStr">
+        <is>
+          <t>변경 후 준공기한</t>
+        </is>
+      </c>
+      <c r="W10" s="5" t="n"/>
+      <c r="X10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="43.5" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>제1회</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="11" t="n">
+        <v>46188</v>
+      </c>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>설계변경 — 배수관 연장 늘어남(실정보고 제3호)</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="12">
+        <f>IF(N11="","",N(G7))</f>
+        <v/>
+      </c>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="7" t="n">
+        <v>48650000</v>
+      </c>
+      <c r="O11" s="5" t="n"/>
+      <c r="P11" s="5" t="n"/>
+      <c r="Q11" s="12">
+        <f>IF(N11="","",K11+N11)</f>
+        <v/>
+      </c>
+      <c r="R11" s="5" t="n"/>
+      <c r="S11" s="5" t="n"/>
+      <c r="T11" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="U11" s="5" t="n"/>
+      <c r="V11" s="14">
+        <f>IF(AND(N11="",T11=""),"",G8+N(T11))</f>
+        <v/>
+      </c>
+      <c r="W11" s="5" t="n"/>
+      <c r="X11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="43.5" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>제2회</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="11" t="n">
+        <v>46254</v>
+      </c>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>물가변동 — 품목조정률 3.42%</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="12">
+        <f>IF(N12="","",N(G7)+SUM(N11:N11))</f>
+        <v/>
+      </c>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="7" t="n">
+        <v>21380000</v>
+      </c>
+      <c r="O12" s="5" t="n"/>
+      <c r="P12" s="5" t="n"/>
+      <c r="Q12" s="12">
+        <f>IF(N12="","",K12+N12)</f>
+        <v/>
+      </c>
+      <c r="R12" s="5" t="n"/>
+      <c r="S12" s="5" t="n"/>
+      <c r="T12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="5" t="n"/>
+      <c r="V12" s="14">
+        <f>IF(AND(N12="",T12=""),"",G8+SUM(T11:T12))</f>
+        <v/>
+      </c>
+      <c r="W12" s="5" t="n"/>
+      <c r="X12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="43.5" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>제3회</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="11" t="n">
+        <v>46290</v>
+      </c>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>설계변경 — 포장 단면 조정(감)</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="12">
+        <f>IF(N13="","",N(G7)+SUM(N11:N12))</f>
+        <v/>
+      </c>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="7" t="n">
+        <v>-6120000</v>
+      </c>
+      <c r="O13" s="5" t="n"/>
+      <c r="P13" s="5" t="n"/>
+      <c r="Q13" s="12">
+        <f>IF(N13="","",K13+N13)</f>
+        <v/>
+      </c>
+      <c r="R13" s="5" t="n"/>
+      <c r="S13" s="5" t="n"/>
+      <c r="T13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="5" t="n"/>
+      <c r="V13" s="14">
+        <f>IF(AND(N13="",T13=""),"",G8+SUM(T11:T13))</f>
+        <v/>
+      </c>
+      <c r="W13" s="5" t="n"/>
+      <c r="X13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="10" t="n"/>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="11" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="12">
+        <f>IF(N14="","",N(G7)+SUM(N11:N13))</f>
+        <v/>
+      </c>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="7" t="n"/>
+      <c r="O14" s="5" t="n"/>
+      <c r="P14" s="5" t="n"/>
+      <c r="Q14" s="12">
+        <f>IF(N14="","",K14+N14)</f>
+        <v/>
+      </c>
+      <c r="R14" s="5" t="n"/>
+      <c r="S14" s="5" t="n"/>
+      <c r="T14" s="13" t="n"/>
+      <c r="U14" s="5" t="n"/>
+      <c r="V14" s="14">
+        <f>IF(AND(N14="",T14=""),"",G8+SUM(T11:T14))</f>
+        <v/>
+      </c>
+      <c r="W14" s="5" t="n"/>
+      <c r="X14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="10" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="11" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="10" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="12">
+        <f>IF(N15="","",N(G7)+SUM(N11:N14))</f>
+        <v/>
+      </c>
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="7" t="n"/>
+      <c r="O15" s="5" t="n"/>
+      <c r="P15" s="5" t="n"/>
+      <c r="Q15" s="12">
+        <f>IF(N15="","",K15+N15)</f>
+        <v/>
+      </c>
+      <c r="R15" s="5" t="n"/>
+      <c r="S15" s="5" t="n"/>
+      <c r="T15" s="13" t="n"/>
+      <c r="U15" s="5" t="n"/>
+      <c r="V15" s="14">
+        <f>IF(AND(N15="",T15=""),"",G8+SUM(T11:T15))</f>
+        <v/>
+      </c>
+      <c r="W15" s="5" t="n"/>
+      <c r="X15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="10" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="11" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="10" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="12">
+        <f>IF(N16="","",N(G7)+SUM(N11:N15))</f>
+        <v/>
+      </c>
+      <c r="L16" s="5" t="n"/>
+      <c r="M16" s="5" t="n"/>
+      <c r="N16" s="7" t="n"/>
+      <c r="O16" s="5" t="n"/>
+      <c r="P16" s="5" t="n"/>
+      <c r="Q16" s="12">
+        <f>IF(N16="","",K16+N16)</f>
+        <v/>
+      </c>
+      <c r="R16" s="5" t="n"/>
+      <c r="S16" s="5" t="n"/>
+      <c r="T16" s="13" t="n"/>
+      <c r="U16" s="5" t="n"/>
+      <c r="V16" s="14">
+        <f>IF(AND(N16="",T16=""),"",G8+SUM(T11:T16))</f>
+        <v/>
+      </c>
+      <c r="W16" s="5" t="n"/>
+      <c r="X16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="10" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="11" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="10" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="12">
+        <f>IF(N17="","",N(G7)+SUM(N11:N16))</f>
+        <v/>
+      </c>
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="5" t="n"/>
+      <c r="N17" s="7" t="n"/>
+      <c r="O17" s="5" t="n"/>
+      <c r="P17" s="5" t="n"/>
+      <c r="Q17" s="12">
+        <f>IF(N17="","",K17+N17)</f>
+        <v/>
+      </c>
+      <c r="R17" s="5" t="n"/>
+      <c r="S17" s="5" t="n"/>
+      <c r="T17" s="13" t="n"/>
+      <c r="U17" s="5" t="n"/>
+      <c r="V17" s="14">
+        <f>IF(AND(N17="",T17=""),"",G8+SUM(T11:T17))</f>
+        <v/>
+      </c>
+      <c r="W17" s="5" t="n"/>
+      <c r="X17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="10" t="n"/>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="11" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="10" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="12">
+        <f>IF(N18="","",N(G7)+SUM(N11:N17))</f>
+        <v/>
+      </c>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="7" t="n"/>
+      <c r="O18" s="5" t="n"/>
+      <c r="P18" s="5" t="n"/>
+      <c r="Q18" s="12">
+        <f>IF(N18="","",K18+N18)</f>
+        <v/>
+      </c>
+      <c r="R18" s="5" t="n"/>
+      <c r="S18" s="5" t="n"/>
+      <c r="T18" s="13" t="n"/>
+      <c r="U18" s="5" t="n"/>
+      <c r="V18" s="14">
+        <f>IF(AND(N18="",T18=""),"",G8+SUM(T11:T18))</f>
+        <v/>
+      </c>
+      <c r="W18" s="5" t="n"/>
+      <c r="X18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="10" t="n"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="11" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="10" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="12">
+        <f>IF(N19="","",N(G7)+SUM(N11:N18))</f>
+        <v/>
+      </c>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="7" t="n"/>
+      <c r="O19" s="5" t="n"/>
+      <c r="P19" s="5" t="n"/>
+      <c r="Q19" s="12">
+        <f>IF(N19="","",K19+N19)</f>
+        <v/>
+      </c>
+      <c r="R19" s="5" t="n"/>
+      <c r="S19" s="5" t="n"/>
+      <c r="T19" s="13" t="n"/>
+      <c r="U19" s="5" t="n"/>
+      <c r="V19" s="14">
+        <f>IF(AND(N19="",T19=""),"",G8+SUM(T11:T19))</f>
+        <v/>
+      </c>
+      <c r="W19" s="5" t="n"/>
+      <c r="X19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="10" t="n"/>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="11" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="10" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="12">
+        <f>IF(N20="","",N(G7)+SUM(N11:N19))</f>
+        <v/>
+      </c>
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="n"/>
+      <c r="N20" s="7" t="n"/>
+      <c r="O20" s="5" t="n"/>
+      <c r="P20" s="5" t="n"/>
+      <c r="Q20" s="12">
+        <f>IF(N20="","",K20+N20)</f>
+        <v/>
+      </c>
+      <c r="R20" s="5" t="n"/>
+      <c r="S20" s="5" t="n"/>
+      <c r="T20" s="13" t="n"/>
+      <c r="U20" s="5" t="n"/>
+      <c r="V20" s="14">
+        <f>IF(AND(N20="",T20=""),"",G8+SUM(T11:T20))</f>
+        <v/>
+      </c>
+      <c r="W20" s="5" t="n"/>
+      <c r="X20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="10" t="n"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="11" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="10" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="12">
+        <f>IF(N21="","",N(G7)+SUM(N11:N20))</f>
+        <v/>
+      </c>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="7" t="n"/>
+      <c r="O21" s="5" t="n"/>
+      <c r="P21" s="5" t="n"/>
+      <c r="Q21" s="12">
+        <f>IF(N21="","",K21+N21)</f>
+        <v/>
+      </c>
+      <c r="R21" s="5" t="n"/>
+      <c r="S21" s="5" t="n"/>
+      <c r="T21" s="13" t="n"/>
+      <c r="U21" s="5" t="n"/>
+      <c r="V21" s="14">
+        <f>IF(AND(N21="",T21=""),"",G8+SUM(T11:T21))</f>
+        <v/>
+      </c>
+      <c r="W21" s="5" t="n"/>
+      <c r="X21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="10" t="n"/>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="11" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="10" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="12">
+        <f>IF(N22="","",N(G7)+SUM(N11:N21))</f>
+        <v/>
+      </c>
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="5" t="n"/>
+      <c r="N22" s="7" t="n"/>
+      <c r="O22" s="5" t="n"/>
+      <c r="P22" s="5" t="n"/>
+      <c r="Q22" s="12">
+        <f>IF(N22="","",K22+N22)</f>
+        <v/>
+      </c>
+      <c r="R22" s="5" t="n"/>
+      <c r="S22" s="5" t="n"/>
+      <c r="T22" s="13" t="n"/>
+      <c r="U22" s="5" t="n"/>
+      <c r="V22" s="14">
+        <f>IF(AND(N22="",T22=""),"",G8+SUM(T11:T22))</f>
+        <v/>
+      </c>
+      <c r="W22" s="5" t="n"/>
+      <c r="X22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="6" customHeight="1"/>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>※ 사유는 설계변경 / 물가변동 / 공기연장 으로 나누어 적습니다 — 근거 법령이 다릅니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="6" customHeight="1"/>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  증액 누계</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="12">
+        <f>SUMIF(N11:N22,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="5" t="n"/>
+      <c r="L26" s="5" t="n"/>
+      <c r="M26" s="5" t="n"/>
+      <c r="N26" s="5" t="n"/>
+      <c r="O26" s="5" t="n"/>
+      <c r="P26" s="5" t="n"/>
+      <c r="Q26" s="5" t="n"/>
+      <c r="R26" s="5" t="n"/>
+      <c r="S26" s="5" t="n"/>
+      <c r="T26" s="5" t="n"/>
+      <c r="U26" s="5" t="n"/>
+      <c r="V26" s="5" t="n"/>
+      <c r="W26" s="5" t="n"/>
+      <c r="X26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  감액 누계</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="12">
+        <f>SUMIF(N11:N22,"&lt;0")</f>
+        <v/>
+      </c>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="5" t="n"/>
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="5" t="n"/>
+      <c r="N27" s="5" t="n"/>
+      <c r="O27" s="5" t="n"/>
+      <c r="P27" s="5" t="n"/>
+      <c r="Q27" s="5" t="n"/>
+      <c r="R27" s="5" t="n"/>
+      <c r="S27" s="5" t="n"/>
+      <c r="T27" s="5" t="n"/>
+      <c r="U27" s="5" t="n"/>
+      <c r="V27" s="5" t="n"/>
+      <c r="W27" s="5" t="n"/>
+      <c r="X27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  현재 계약금액</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="12">
+        <f>N(G7)+SUM(N11:N22)</f>
+        <v/>
+      </c>
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="n"/>
+      <c r="K28" s="5" t="n"/>
+      <c r="L28" s="5" t="n"/>
+      <c r="M28" s="5" t="n"/>
+      <c r="N28" s="5" t="n"/>
+      <c r="O28" s="5" t="n"/>
+      <c r="P28" s="5" t="n"/>
+      <c r="Q28" s="5" t="n"/>
+      <c r="R28" s="5" t="n"/>
+      <c r="S28" s="5" t="n"/>
+      <c r="T28" s="5" t="n"/>
+      <c r="U28" s="5" t="n"/>
+      <c r="V28" s="5" t="n"/>
+      <c r="W28" s="5" t="n"/>
+      <c r="X28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  최초 대비 증감률</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="16">
+        <f>IF(N(G7)=0,"",SUM(N11:N22)/G7)</f>
+        <v/>
+      </c>
+      <c r="H29" s="5" t="n"/>
+      <c r="I29" s="5" t="n"/>
+      <c r="J29" s="5" t="n"/>
+      <c r="K29" s="5" t="n"/>
+      <c r="L29" s="5" t="n"/>
+      <c r="M29" s="5" t="n"/>
+      <c r="N29" s="5" t="n"/>
+      <c r="O29" s="5" t="n"/>
+      <c r="P29" s="5" t="n"/>
+      <c r="Q29" s="5" t="n"/>
+      <c r="R29" s="5" t="n"/>
+      <c r="S29" s="5" t="n"/>
+      <c r="T29" s="5" t="n"/>
+      <c r="U29" s="5" t="n"/>
+      <c r="V29" s="5" t="n"/>
+      <c r="W29" s="5" t="n"/>
+      <c r="X29" s="5" t="n"/>
+    </row>
+    <row r="30" ht="6" customHeight="1"/>
+    <row r="31" ht="10" customHeight="1"/>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="17" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="18" t="inlineStr"/>
+      <c r="K33" s="19" t="inlineStr">
+        <is>
+          <t>현장대리인</t>
+        </is>
+      </c>
+      <c r="Q33" s="20" t="inlineStr">
+        <is>
+          <t>김철수</t>
+        </is>
+      </c>
+      <c r="U33" s="21" t="inlineStr">
+        <is>
+          <t>(서명 또는 인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="18" t="inlineStr"/>
+      <c r="K34" s="19" t="inlineStr">
+        <is>
+          <t>감독</t>
+        </is>
+      </c>
+      <c r="Q34" s="20" t="inlineStr">
+        <is>
+          <t>박감독</t>
+        </is>
+      </c>
+      <c r="U34" s="21" t="inlineStr">
+        <is>
+          <t>(서명 또는 인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="18" t="inlineStr"/>
+      <c r="K35" s="19" t="inlineStr">
+        <is>
+          <t>발주기관</t>
+        </is>
+      </c>
+      <c r="Q35" s="20" t="inlineStr">
+        <is>
+          <t>건설과장</t>
+        </is>
+      </c>
+      <c r="U35" s="21" t="inlineStr">
+        <is>
+          <t>(서명 또는 인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="6" customHeight="1"/>
+    <row r="38" ht="19.5" customHeight="1">
+      <c r="A38" s="22" t="inlineStr">
+        <is>
+          <t>이 시트는 작성 예시입니다(가상의 현장 · 이름 · 금액). 실제로는 앞 시트에 적으세요.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="138">
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="Q14:S14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="F10:J10"/>
+    <mergeCell ref="F19:J19"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="A3:X3"/>
+    <mergeCell ref="Q15:S15"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="F18:J18"/>
+    <mergeCell ref="K17:M17"/>
+    <mergeCell ref="A32:X32"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="F17:J17"/>
+    <mergeCell ref="T12:U12"/>
+    <mergeCell ref="V22:X22"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="G29:X29"/>
+    <mergeCell ref="A38:X38"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="V12:X12"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="V21:X21"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="K33:P33"/>
+    <mergeCell ref="V14:X14"/>
+    <mergeCell ref="Q35:T35"/>
+    <mergeCell ref="A24:X24"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="Q34:T34"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="K35:P35"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:X7"/>
+    <mergeCell ref="Q19:S19"/>
+    <mergeCell ref="K22:M22"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="F21:J21"/>
+    <mergeCell ref="T10:U10"/>
+    <mergeCell ref="Q22:S22"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="G26:X26"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="T11:U11"/>
+    <mergeCell ref="Q13:S13"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="F22:J22"/>
+    <mergeCell ref="V17:X17"/>
+    <mergeCell ref="Q16:S16"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="T22:U22"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="Q18:S18"/>
+    <mergeCell ref="V20:X20"/>
+    <mergeCell ref="F14:J14"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="U33:X33"/>
+    <mergeCell ref="F11:J11"/>
+    <mergeCell ref="T15:U15"/>
+    <mergeCell ref="Q10:S10"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="V15:X15"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="F15:J15"/>
+    <mergeCell ref="F12:J12"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="Q17:S17"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="V16:X16"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="V18:X18"/>
+    <mergeCell ref="T17:U17"/>
+    <mergeCell ref="Q12:S12"/>
+    <mergeCell ref="K15:M15"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="Q21:S21"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="T19:U19"/>
+    <mergeCell ref="G27:X27"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="A33:J33"/>
+    <mergeCell ref="V19:X19"/>
+    <mergeCell ref="F16:J16"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="T14:U14"/>
+    <mergeCell ref="G28:X28"/>
+    <mergeCell ref="A35:J35"/>
+    <mergeCell ref="G6:X6"/>
+    <mergeCell ref="V11:X11"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="U35:X35"/>
+    <mergeCell ref="F20:J20"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="G5:X5"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="U34:X34"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="T21:U21"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="Q11:S11"/>
+    <mergeCell ref="Q33:T33"/>
+    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="T13:U13"/>
+    <mergeCell ref="K34:P34"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="T16:U16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="M1:X1"/>
+    <mergeCell ref="T18:U18"/>
+    <mergeCell ref="G8:X8"/>
+    <mergeCell ref="Q20:S20"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/web/public/forms/chg-chongwal.xlsx
+++ b/web/public/forms/chg-chongwal.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'설계변경 총괄표'!$A$1:$X$36</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$X$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'설계변경 총괄표'!$A$1:$X$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$X$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -564,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:X39"/>
+  <dimension ref="A1:X37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.6" customWidth="1" min="1" max="1"/>
@@ -1143,89 +1143,85 @@
       <c r="W20" s="5" t="n"/>
       <c r="X20" s="5" t="n"/>
     </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="10" t="n"/>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="11" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="10" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="12">
-        <f>IF(N21="","",N(G7)+SUM(N11:N20))</f>
-        <v/>
-      </c>
-      <c r="L21" s="5" t="n"/>
-      <c r="M21" s="5" t="n"/>
-      <c r="N21" s="7" t="n"/>
-      <c r="O21" s="5" t="n"/>
-      <c r="P21" s="5" t="n"/>
-      <c r="Q21" s="12">
-        <f>IF(N21="","",K21+N21)</f>
-        <v/>
-      </c>
-      <c r="R21" s="5" t="n"/>
-      <c r="S21" s="5" t="n"/>
-      <c r="T21" s="13" t="n"/>
-      <c r="U21" s="5" t="n"/>
-      <c r="V21" s="14">
-        <f>IF(AND(N21="",T21=""),"",G8+SUM(T11:T21))</f>
-        <v/>
-      </c>
-      <c r="W21" s="5" t="n"/>
-      <c r="X21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="10" t="n"/>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="11" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="10" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="12">
-        <f>IF(N22="","",N(G7)+SUM(N11:N21))</f>
-        <v/>
-      </c>
-      <c r="L22" s="5" t="n"/>
-      <c r="M22" s="5" t="n"/>
-      <c r="N22" s="7" t="n"/>
-      <c r="O22" s="5" t="n"/>
-      <c r="P22" s="5" t="n"/>
-      <c r="Q22" s="12">
-        <f>IF(N22="","",K22+N22)</f>
-        <v/>
-      </c>
-      <c r="R22" s="5" t="n"/>
-      <c r="S22" s="5" t="n"/>
-      <c r="T22" s="13" t="n"/>
-      <c r="U22" s="5" t="n"/>
-      <c r="V22" s="14">
-        <f>IF(AND(N22="",T22=""),"",G8+SUM(T11:T22))</f>
-        <v/>
-      </c>
-      <c r="W22" s="5" t="n"/>
-      <c r="X22" s="5" t="n"/>
+    <row r="21" ht="6" customHeight="1"/>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>※ 사유는 설계변경 / 물가변동 / 공기연장 으로 나누어 적습니다 — 근거 법령이 다릅니다.</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="6" customHeight="1"/>
-    <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>※ 사유는 설계변경 / 물가변동 / 공기연장 으로 나누어 적습니다 — 근거 법령이 다릅니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="6" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  증액 누계</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="12">
+        <f>SUMIF(N11:N20,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="n"/>
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="n"/>
+      <c r="N24" s="5" t="n"/>
+      <c r="O24" s="5" t="n"/>
+      <c r="P24" s="5" t="n"/>
+      <c r="Q24" s="5" t="n"/>
+      <c r="R24" s="5" t="n"/>
+      <c r="S24" s="5" t="n"/>
+      <c r="T24" s="5" t="n"/>
+      <c r="U24" s="5" t="n"/>
+      <c r="V24" s="5" t="n"/>
+      <c r="W24" s="5" t="n"/>
+      <c r="X24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  감액 누계</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="12">
+        <f>SUMIF(N11:N20,"&lt;0")</f>
+        <v/>
+      </c>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="5" t="n"/>
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="5" t="n"/>
+      <c r="N25" s="5" t="n"/>
+      <c r="O25" s="5" t="n"/>
+      <c r="P25" s="5" t="n"/>
+      <c r="Q25" s="5" t="n"/>
+      <c r="R25" s="5" t="n"/>
+      <c r="S25" s="5" t="n"/>
+      <c r="T25" s="5" t="n"/>
+      <c r="U25" s="5" t="n"/>
+      <c r="V25" s="5" t="n"/>
+      <c r="W25" s="5" t="n"/>
+      <c r="X25" s="5" t="n"/>
+    </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  증액 누계</t>
+          <t xml:space="preserve">  현재 계약금액</t>
         </is>
       </c>
       <c r="B26" s="5" t="n"/>
@@ -1234,7 +1230,7 @@
       <c r="E26" s="5" t="n"/>
       <c r="F26" s="5" t="n"/>
       <c r="G26" s="12">
-        <f>SUMIF(N11:N22,"&gt;0")</f>
+        <f>N(G7)+SUM(N11:N20)</f>
         <v/>
       </c>
       <c r="H26" s="5" t="n"/>
@@ -1258,7 +1254,7 @@
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  감액 누계</t>
+          <t xml:space="preserve">  최초 대비 증감률</t>
         </is>
       </c>
       <c r="B27" s="5" t="n"/>
@@ -1266,8 +1262,8 @@
       <c r="D27" s="5" t="n"/>
       <c r="E27" s="5" t="n"/>
       <c r="F27" s="5" t="n"/>
-      <c r="G27" s="12">
-        <f>SUMIF(N11:N22,"&lt;0")</f>
+      <c r="G27" s="16">
+        <f>IF(N(G7)=0,"",SUM(N11:N20)/G7)</f>
         <v/>
       </c>
       <c r="H27" s="5" t="n"/>
@@ -1288,78 +1284,40 @@
       <c r="W27" s="5" t="n"/>
       <c r="X27" s="5" t="n"/>
     </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  현재 계약금액</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="n"/>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="12">
-        <f>N(G7)+SUM(N11:N22)</f>
-        <v/>
-      </c>
-      <c r="H28" s="5" t="n"/>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="5" t="n"/>
-      <c r="K28" s="5" t="n"/>
-      <c r="L28" s="5" t="n"/>
-      <c r="M28" s="5" t="n"/>
-      <c r="N28" s="5" t="n"/>
-      <c r="O28" s="5" t="n"/>
-      <c r="P28" s="5" t="n"/>
-      <c r="Q28" s="5" t="n"/>
-      <c r="R28" s="5" t="n"/>
-      <c r="S28" s="5" t="n"/>
-      <c r="T28" s="5" t="n"/>
-      <c r="U28" s="5" t="n"/>
-      <c r="V28" s="5" t="n"/>
-      <c r="W28" s="5" t="n"/>
-      <c r="X28" s="5" t="n"/>
-    </row>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  최초 대비 증감률</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="5" t="n"/>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="16">
-        <f>IF(N(G7)=0,"",SUM(N11:N22)/G7)</f>
-        <v/>
-      </c>
-      <c r="H29" s="5" t="n"/>
-      <c r="I29" s="5" t="n"/>
-      <c r="J29" s="5" t="n"/>
-      <c r="K29" s="5" t="n"/>
-      <c r="L29" s="5" t="n"/>
-      <c r="M29" s="5" t="n"/>
-      <c r="N29" s="5" t="n"/>
-      <c r="O29" s="5" t="n"/>
-      <c r="P29" s="5" t="n"/>
-      <c r="Q29" s="5" t="n"/>
-      <c r="R29" s="5" t="n"/>
-      <c r="S29" s="5" t="n"/>
-      <c r="T29" s="5" t="n"/>
-      <c r="U29" s="5" t="n"/>
-      <c r="V29" s="5" t="n"/>
-      <c r="W29" s="5" t="n"/>
-      <c r="X29" s="5" t="n"/>
-    </row>
-    <row r="30" ht="6" customHeight="1"/>
-    <row r="31" ht="10" customHeight="1"/>
-    <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="17" t="inlineStr">
+    <row r="28" ht="6" customHeight="1"/>
+    <row r="29" ht="10" customHeight="1"/>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">          년        월        일</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="18" t="inlineStr"/>
+      <c r="K31" s="19" t="inlineStr">
+        <is>
+          <t>현장대리인</t>
+        </is>
+      </c>
+      <c r="Q31" s="20" t="n"/>
+      <c r="U31" s="21" t="inlineStr">
+        <is>
+          <t>(서명 또는 인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="18" t="inlineStr"/>
+      <c r="K32" s="19" t="inlineStr">
+        <is>
+          <t>감독</t>
+        </is>
+      </c>
+      <c r="Q32" s="20" t="n"/>
+      <c r="U32" s="21" t="inlineStr">
+        <is>
+          <t>(서명 또는 인)</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1325,7 @@
       <c r="A33" s="18" t="inlineStr"/>
       <c r="K33" s="19" t="inlineStr">
         <is>
-          <t>현장대리인</t>
+          <t>발주기관</t>
         </is>
       </c>
       <c r="Q33" s="20" t="n"/>
@@ -1377,124 +1335,86 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="18" t="inlineStr"/>
-      <c r="K34" s="19" t="inlineStr">
-        <is>
-          <t>감독</t>
-        </is>
-      </c>
-      <c r="Q34" s="20" t="n"/>
-      <c r="U34" s="21" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="18" t="inlineStr"/>
-      <c r="K35" s="19" t="inlineStr">
-        <is>
-          <t>발주기관</t>
-        </is>
-      </c>
-      <c r="Q35" s="20" t="n"/>
-      <c r="U35" s="21" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="6" customHeight="1"/>
-    <row r="38" ht="34" customHeight="1">
-      <c r="A38" s="22" t="inlineStr">
+    <row r="34" ht="6" customHeight="1"/>
+    <row r="36" ht="34" customHeight="1">
+      <c r="A36" s="22" t="inlineStr">
         <is>
           <t>노란 칸 = 요율·기준값(발주기관 기준으로 고쳐 씀) · 옅은 하늘색 칸 = 자동 계산(지우지 마세요) · 뒤 시트에 «작성 예시» 가 있습니다.</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="19.5" customHeight="1">
-      <c r="A39" s="22" t="inlineStr">
+    <row r="37" ht="19.5" customHeight="1">
+      <c r="A37" s="22" t="inlineStr">
         <is>
           <t>발주기관이 정한 서식이 있으면 그 서식을 쓰세요. 이 줄과 1행은 지워도 됩니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="139">
+  <mergeCells count="123">
     <mergeCell ref="V10:X10"/>
     <mergeCell ref="Q14:S14"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="F10:J10"/>
     <mergeCell ref="F19:J19"/>
     <mergeCell ref="N17:P17"/>
-    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="K31:P31"/>
     <mergeCell ref="A3:X3"/>
     <mergeCell ref="Q15:S15"/>
     <mergeCell ref="N19:P19"/>
+    <mergeCell ref="U31:X31"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A34:J34"/>
     <mergeCell ref="F18:J18"/>
     <mergeCell ref="K17:M17"/>
-    <mergeCell ref="A32:X32"/>
-    <mergeCell ref="A29:F29"/>
     <mergeCell ref="F17:J17"/>
     <mergeCell ref="T12:U12"/>
-    <mergeCell ref="V22:X22"/>
     <mergeCell ref="K10:M10"/>
-    <mergeCell ref="G29:X29"/>
-    <mergeCell ref="A38:X38"/>
     <mergeCell ref="C18:E18"/>
     <mergeCell ref="V12:X12"/>
     <mergeCell ref="A17:B17"/>
-    <mergeCell ref="V21:X21"/>
     <mergeCell ref="K16:M16"/>
-    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="K33:P33"/>
     <mergeCell ref="V14:X14"/>
-    <mergeCell ref="Q35:T35"/>
-    <mergeCell ref="A24:X24"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="V13:X13"/>
-    <mergeCell ref="Q34:T34"/>
     <mergeCell ref="K20:M20"/>
-    <mergeCell ref="K35:P35"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="K11:M11"/>
     <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A32:J32"/>
     <mergeCell ref="G7:X7"/>
     <mergeCell ref="Q19:S19"/>
-    <mergeCell ref="K22:M22"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="N18:P18"/>
-    <mergeCell ref="C22:E22"/>
     <mergeCell ref="A27:F27"/>
     <mergeCell ref="K12:M12"/>
     <mergeCell ref="C12:E12"/>
-    <mergeCell ref="F21:J21"/>
     <mergeCell ref="T10:U10"/>
-    <mergeCell ref="Q22:S22"/>
+    <mergeCell ref="G24:X24"/>
+    <mergeCell ref="A31:J31"/>
     <mergeCell ref="N10:P10"/>
     <mergeCell ref="K14:M14"/>
+    <mergeCell ref="A25:F25"/>
     <mergeCell ref="G26:X26"/>
-    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A22:X22"/>
     <mergeCell ref="C13:E13"/>
     <mergeCell ref="T11:U11"/>
+    <mergeCell ref="G25:X25"/>
     <mergeCell ref="Q13:S13"/>
     <mergeCell ref="K18:M18"/>
-    <mergeCell ref="F22:J22"/>
     <mergeCell ref="V17:X17"/>
     <mergeCell ref="Q16:S16"/>
     <mergeCell ref="C15:E15"/>
     <mergeCell ref="N20:P20"/>
-    <mergeCell ref="T22:U22"/>
-    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="U32:X32"/>
+    <mergeCell ref="A30:X30"/>
+    <mergeCell ref="Q31:T31"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="Q18:S18"/>
     <mergeCell ref="V20:X20"/>
     <mergeCell ref="F14:J14"/>
     <mergeCell ref="N12:P12"/>
-    <mergeCell ref="N21:P21"/>
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="U33:X33"/>
@@ -1511,7 +1431,6 @@
     <mergeCell ref="Q17:S17"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="V16:X16"/>
-    <mergeCell ref="A21:B21"/>
     <mergeCell ref="K13:M13"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="V18:X18"/>
@@ -1519,30 +1438,25 @@
     <mergeCell ref="Q12:S12"/>
     <mergeCell ref="K15:M15"/>
     <mergeCell ref="N11:P11"/>
-    <mergeCell ref="Q21:S21"/>
     <mergeCell ref="C14:E14"/>
-    <mergeCell ref="A39:X39"/>
     <mergeCell ref="T19:U19"/>
     <mergeCell ref="G27:X27"/>
-    <mergeCell ref="K21:M21"/>
     <mergeCell ref="A33:J33"/>
     <mergeCell ref="V19:X19"/>
+    <mergeCell ref="K32:P32"/>
     <mergeCell ref="F16:J16"/>
     <mergeCell ref="T20:U20"/>
     <mergeCell ref="T14:U14"/>
-    <mergeCell ref="G28:X28"/>
-    <mergeCell ref="A35:J35"/>
     <mergeCell ref="G6:X6"/>
+    <mergeCell ref="A37:X37"/>
+    <mergeCell ref="Q32:T32"/>
     <mergeCell ref="V11:X11"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="U35:X35"/>
     <mergeCell ref="F20:J20"/>
     <mergeCell ref="N13:P13"/>
     <mergeCell ref="G5:X5"/>
     <mergeCell ref="C17:E17"/>
-    <mergeCell ref="U34:X34"/>
     <mergeCell ref="A18:B18"/>
-    <mergeCell ref="T21:U21"/>
     <mergeCell ref="N15:P15"/>
     <mergeCell ref="Q11:S11"/>
     <mergeCell ref="Q33:T33"/>
@@ -1550,7 +1464,6 @@
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="F13:J13"/>
     <mergeCell ref="T13:U13"/>
-    <mergeCell ref="K34:P34"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="T16:U16"/>
     <mergeCell ref="N16:P16"/>
@@ -1559,6 +1472,7 @@
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="M1:X1"/>
     <mergeCell ref="T18:U18"/>
+    <mergeCell ref="A36:X36"/>
     <mergeCell ref="G8:X8"/>
     <mergeCell ref="Q20:S20"/>
   </mergeCells>
@@ -1575,7 +1489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:X38"/>
+  <dimension ref="A1:X36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.6" customWidth="1" min="1" max="1"/>
@@ -1816,7 +1730,7 @@
       <c r="W10" s="5" t="n"/>
       <c r="X10" s="5" t="n"/>
     </row>
-    <row r="11" ht="43.5" customHeight="1">
+    <row r="11" ht="45" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
           <t>제1회</t>
@@ -1865,7 +1779,7 @@
       <c r="W11" s="5" t="n"/>
       <c r="X11" s="5" t="n"/>
     </row>
-    <row r="12" ht="43.5" customHeight="1">
+    <row r="12" ht="32" customHeight="1">
       <c r="A12" s="10" t="inlineStr">
         <is>
           <t>제2회</t>
@@ -1914,7 +1828,7 @@
       <c r="W12" s="5" t="n"/>
       <c r="X12" s="5" t="n"/>
     </row>
-    <row r="13" ht="43.5" customHeight="1">
+    <row r="13" ht="32" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
           <t>제3회</t>
@@ -2208,89 +2122,85 @@
       <c r="W20" s="5" t="n"/>
       <c r="X20" s="5" t="n"/>
     </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="10" t="n"/>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="11" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="10" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="12">
-        <f>IF(N21="","",N(G7)+SUM(N11:N20))</f>
-        <v/>
-      </c>
-      <c r="L21" s="5" t="n"/>
-      <c r="M21" s="5" t="n"/>
-      <c r="N21" s="7" t="n"/>
-      <c r="O21" s="5" t="n"/>
-      <c r="P21" s="5" t="n"/>
-      <c r="Q21" s="12">
-        <f>IF(N21="","",K21+N21)</f>
-        <v/>
-      </c>
-      <c r="R21" s="5" t="n"/>
-      <c r="S21" s="5" t="n"/>
-      <c r="T21" s="13" t="n"/>
-      <c r="U21" s="5" t="n"/>
-      <c r="V21" s="14">
-        <f>IF(AND(N21="",T21=""),"",G8+SUM(T11:T21))</f>
-        <v/>
-      </c>
-      <c r="W21" s="5" t="n"/>
-      <c r="X21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="10" t="n"/>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="11" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="10" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="12">
-        <f>IF(N22="","",N(G7)+SUM(N11:N21))</f>
-        <v/>
-      </c>
-      <c r="L22" s="5" t="n"/>
-      <c r="M22" s="5" t="n"/>
-      <c r="N22" s="7" t="n"/>
-      <c r="O22" s="5" t="n"/>
-      <c r="P22" s="5" t="n"/>
-      <c r="Q22" s="12">
-        <f>IF(N22="","",K22+N22)</f>
-        <v/>
-      </c>
-      <c r="R22" s="5" t="n"/>
-      <c r="S22" s="5" t="n"/>
-      <c r="T22" s="13" t="n"/>
-      <c r="U22" s="5" t="n"/>
-      <c r="V22" s="14">
-        <f>IF(AND(N22="",T22=""),"",G8+SUM(T11:T22))</f>
-        <v/>
-      </c>
-      <c r="W22" s="5" t="n"/>
-      <c r="X22" s="5" t="n"/>
+    <row r="21" ht="6" customHeight="1"/>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>※ 사유는 설계변경 / 물가변동 / 공기연장 으로 나누어 적습니다 — 근거 법령이 다릅니다.</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="6" customHeight="1"/>
-    <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>※ 사유는 설계변경 / 물가변동 / 공기연장 으로 나누어 적습니다 — 근거 법령이 다릅니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="6" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  증액 누계</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="12">
+        <f>SUMIF(N11:N20,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="n"/>
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="n"/>
+      <c r="N24" s="5" t="n"/>
+      <c r="O24" s="5" t="n"/>
+      <c r="P24" s="5" t="n"/>
+      <c r="Q24" s="5" t="n"/>
+      <c r="R24" s="5" t="n"/>
+      <c r="S24" s="5" t="n"/>
+      <c r="T24" s="5" t="n"/>
+      <c r="U24" s="5" t="n"/>
+      <c r="V24" s="5" t="n"/>
+      <c r="W24" s="5" t="n"/>
+      <c r="X24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  감액 누계</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="12">
+        <f>SUMIF(N11:N20,"&lt;0")</f>
+        <v/>
+      </c>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="5" t="n"/>
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="5" t="n"/>
+      <c r="N25" s="5" t="n"/>
+      <c r="O25" s="5" t="n"/>
+      <c r="P25" s="5" t="n"/>
+      <c r="Q25" s="5" t="n"/>
+      <c r="R25" s="5" t="n"/>
+      <c r="S25" s="5" t="n"/>
+      <c r="T25" s="5" t="n"/>
+      <c r="U25" s="5" t="n"/>
+      <c r="V25" s="5" t="n"/>
+      <c r="W25" s="5" t="n"/>
+      <c r="X25" s="5" t="n"/>
+    </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  증액 누계</t>
+          <t xml:space="preserve">  현재 계약금액</t>
         </is>
       </c>
       <c r="B26" s="5" t="n"/>
@@ -2299,7 +2209,7 @@
       <c r="E26" s="5" t="n"/>
       <c r="F26" s="5" t="n"/>
       <c r="G26" s="12">
-        <f>SUMIF(N11:N22,"&gt;0")</f>
+        <f>N(G7)+SUM(N11:N20)</f>
         <v/>
       </c>
       <c r="H26" s="5" t="n"/>
@@ -2323,7 +2233,7 @@
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  감액 누계</t>
+          <t xml:space="preserve">  최초 대비 증감률</t>
         </is>
       </c>
       <c r="B27" s="5" t="n"/>
@@ -2331,8 +2241,8 @@
       <c r="D27" s="5" t="n"/>
       <c r="E27" s="5" t="n"/>
       <c r="F27" s="5" t="n"/>
-      <c r="G27" s="12">
-        <f>SUMIF(N11:N22,"&lt;0")</f>
+      <c r="G27" s="16">
+        <f>IF(N(G7)=0,"",SUM(N11:N20)/G7)</f>
         <v/>
       </c>
       <c r="H27" s="5" t="n"/>
@@ -2353,89 +2263,59 @@
       <c r="W27" s="5" t="n"/>
       <c r="X27" s="5" t="n"/>
     </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  현재 계약금액</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="n"/>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="12">
-        <f>N(G7)+SUM(N11:N22)</f>
-        <v/>
-      </c>
-      <c r="H28" s="5" t="n"/>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="5" t="n"/>
-      <c r="K28" s="5" t="n"/>
-      <c r="L28" s="5" t="n"/>
-      <c r="M28" s="5" t="n"/>
-      <c r="N28" s="5" t="n"/>
-      <c r="O28" s="5" t="n"/>
-      <c r="P28" s="5" t="n"/>
-      <c r="Q28" s="5" t="n"/>
-      <c r="R28" s="5" t="n"/>
-      <c r="S28" s="5" t="n"/>
-      <c r="T28" s="5" t="n"/>
-      <c r="U28" s="5" t="n"/>
-      <c r="V28" s="5" t="n"/>
-      <c r="W28" s="5" t="n"/>
-      <c r="X28" s="5" t="n"/>
-    </row>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  최초 대비 증감률</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="5" t="n"/>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="16">
-        <f>IF(N(G7)=0,"",SUM(N11:N22)/G7)</f>
-        <v/>
-      </c>
-      <c r="H29" s="5" t="n"/>
-      <c r="I29" s="5" t="n"/>
-      <c r="J29" s="5" t="n"/>
-      <c r="K29" s="5" t="n"/>
-      <c r="L29" s="5" t="n"/>
-      <c r="M29" s="5" t="n"/>
-      <c r="N29" s="5" t="n"/>
-      <c r="O29" s="5" t="n"/>
-      <c r="P29" s="5" t="n"/>
-      <c r="Q29" s="5" t="n"/>
-      <c r="R29" s="5" t="n"/>
-      <c r="S29" s="5" t="n"/>
-      <c r="T29" s="5" t="n"/>
-      <c r="U29" s="5" t="n"/>
-      <c r="V29" s="5" t="n"/>
-      <c r="W29" s="5" t="n"/>
-      <c r="X29" s="5" t="n"/>
-    </row>
-    <row r="30" ht="6" customHeight="1"/>
-    <row r="31" ht="10" customHeight="1"/>
-    <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="17" t="n">
+    <row r="28" ht="6" customHeight="1"/>
+    <row r="29" ht="10" customHeight="1"/>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="17" t="n">
         <v>46294</v>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="18" t="inlineStr"/>
+      <c r="K31" s="19" t="inlineStr">
+        <is>
+          <t>현장대리인</t>
+        </is>
+      </c>
+      <c r="Q31" s="20" t="inlineStr">
+        <is>
+          <t>김철수</t>
+        </is>
+      </c>
+      <c r="U31" s="21" t="inlineStr">
+        <is>
+          <t>(서명 또는 인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="18" t="inlineStr"/>
+      <c r="K32" s="19" t="inlineStr">
+        <is>
+          <t>감독</t>
+        </is>
+      </c>
+      <c r="Q32" s="20" t="inlineStr">
+        <is>
+          <t>박감독</t>
+        </is>
+      </c>
+      <c r="U32" s="21" t="inlineStr">
+        <is>
+          <t>(서명 또는 인)</t>
+        </is>
       </c>
     </row>
     <row r="33" ht="24" customHeight="1">
       <c r="A33" s="18" t="inlineStr"/>
       <c r="K33" s="19" t="inlineStr">
         <is>
-          <t>현장대리인</t>
+          <t>발주기관</t>
         </is>
       </c>
       <c r="Q33" s="20" t="inlineStr">
         <is>
-          <t>김철수</t>
+          <t>건설과장</t>
         </is>
       </c>
       <c r="U33" s="21" t="inlineStr">
@@ -2444,125 +2324,79 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="18" t="inlineStr"/>
-      <c r="K34" s="19" t="inlineStr">
-        <is>
-          <t>감독</t>
-        </is>
-      </c>
-      <c r="Q34" s="20" t="inlineStr">
-        <is>
-          <t>박감독</t>
-        </is>
-      </c>
-      <c r="U34" s="21" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="18" t="inlineStr"/>
-      <c r="K35" s="19" t="inlineStr">
-        <is>
-          <t>발주기관</t>
-        </is>
-      </c>
-      <c r="Q35" s="20" t="inlineStr">
-        <is>
-          <t>건설과장</t>
-        </is>
-      </c>
-      <c r="U35" s="21" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="6" customHeight="1"/>
-    <row r="38" ht="19.5" customHeight="1">
-      <c r="A38" s="22" t="inlineStr">
+    <row r="34" ht="6" customHeight="1"/>
+    <row r="36" ht="19.5" customHeight="1">
+      <c r="A36" s="22" t="inlineStr">
         <is>
           <t>이 시트는 작성 예시입니다(가상의 현장 · 이름 · 금액). 실제로는 앞 시트에 적으세요.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="138">
+  <mergeCells count="122">
     <mergeCell ref="V10:X10"/>
     <mergeCell ref="Q14:S14"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="F10:J10"/>
     <mergeCell ref="F19:J19"/>
     <mergeCell ref="N17:P17"/>
-    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="K31:P31"/>
     <mergeCell ref="A3:X3"/>
     <mergeCell ref="Q15:S15"/>
     <mergeCell ref="N19:P19"/>
+    <mergeCell ref="U31:X31"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A34:J34"/>
     <mergeCell ref="F18:J18"/>
     <mergeCell ref="K17:M17"/>
-    <mergeCell ref="A32:X32"/>
-    <mergeCell ref="A29:F29"/>
     <mergeCell ref="F17:J17"/>
     <mergeCell ref="T12:U12"/>
-    <mergeCell ref="V22:X22"/>
     <mergeCell ref="K10:M10"/>
-    <mergeCell ref="G29:X29"/>
-    <mergeCell ref="A38:X38"/>
     <mergeCell ref="C18:E18"/>
     <mergeCell ref="V12:X12"/>
     <mergeCell ref="A17:B17"/>
-    <mergeCell ref="V21:X21"/>
     <mergeCell ref="K16:M16"/>
-    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="K33:P33"/>
     <mergeCell ref="V14:X14"/>
-    <mergeCell ref="Q35:T35"/>
-    <mergeCell ref="A24:X24"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="V13:X13"/>
-    <mergeCell ref="Q34:T34"/>
     <mergeCell ref="K20:M20"/>
-    <mergeCell ref="K35:P35"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="K11:M11"/>
     <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A32:J32"/>
     <mergeCell ref="G7:X7"/>
     <mergeCell ref="Q19:S19"/>
-    <mergeCell ref="K22:M22"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="N18:P18"/>
-    <mergeCell ref="C22:E22"/>
     <mergeCell ref="A27:F27"/>
     <mergeCell ref="K12:M12"/>
     <mergeCell ref="C12:E12"/>
-    <mergeCell ref="F21:J21"/>
     <mergeCell ref="T10:U10"/>
-    <mergeCell ref="Q22:S22"/>
+    <mergeCell ref="G24:X24"/>
+    <mergeCell ref="A31:J31"/>
     <mergeCell ref="N10:P10"/>
     <mergeCell ref="K14:M14"/>
+    <mergeCell ref="A25:F25"/>
     <mergeCell ref="G26:X26"/>
-    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A22:X22"/>
     <mergeCell ref="C13:E13"/>
     <mergeCell ref="T11:U11"/>
+    <mergeCell ref="G25:X25"/>
     <mergeCell ref="Q13:S13"/>
     <mergeCell ref="K18:M18"/>
-    <mergeCell ref="F22:J22"/>
     <mergeCell ref="V17:X17"/>
     <mergeCell ref="Q16:S16"/>
     <mergeCell ref="C15:E15"/>
     <mergeCell ref="N20:P20"/>
-    <mergeCell ref="T22:U22"/>
-    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="U32:X32"/>
+    <mergeCell ref="A30:X30"/>
+    <mergeCell ref="Q31:T31"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="Q18:S18"/>
     <mergeCell ref="V20:X20"/>
     <mergeCell ref="F14:J14"/>
     <mergeCell ref="N12:P12"/>
-    <mergeCell ref="N21:P21"/>
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="U33:X33"/>
@@ -2579,7 +2413,6 @@
     <mergeCell ref="Q17:S17"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="V16:X16"/>
-    <mergeCell ref="A21:B21"/>
     <mergeCell ref="K13:M13"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="V18:X18"/>
@@ -2587,29 +2420,24 @@
     <mergeCell ref="Q12:S12"/>
     <mergeCell ref="K15:M15"/>
     <mergeCell ref="N11:P11"/>
-    <mergeCell ref="Q21:S21"/>
     <mergeCell ref="C14:E14"/>
     <mergeCell ref="T19:U19"/>
     <mergeCell ref="G27:X27"/>
-    <mergeCell ref="K21:M21"/>
     <mergeCell ref="A33:J33"/>
     <mergeCell ref="V19:X19"/>
+    <mergeCell ref="K32:P32"/>
     <mergeCell ref="F16:J16"/>
     <mergeCell ref="T20:U20"/>
     <mergeCell ref="T14:U14"/>
-    <mergeCell ref="G28:X28"/>
-    <mergeCell ref="A35:J35"/>
     <mergeCell ref="G6:X6"/>
+    <mergeCell ref="Q32:T32"/>
     <mergeCell ref="V11:X11"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="U35:X35"/>
     <mergeCell ref="F20:J20"/>
     <mergeCell ref="N13:P13"/>
     <mergeCell ref="G5:X5"/>
     <mergeCell ref="C17:E17"/>
-    <mergeCell ref="U34:X34"/>
     <mergeCell ref="A18:B18"/>
-    <mergeCell ref="T21:U21"/>
     <mergeCell ref="N15:P15"/>
     <mergeCell ref="Q11:S11"/>
     <mergeCell ref="Q33:T33"/>
@@ -2617,7 +2445,6 @@
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="F13:J13"/>
     <mergeCell ref="T13:U13"/>
-    <mergeCell ref="K34:P34"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="T16:U16"/>
     <mergeCell ref="N16:P16"/>
@@ -2626,11 +2453,12 @@
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="M1:X1"/>
     <mergeCell ref="T18:U18"/>
+    <mergeCell ref="A36:X36"/>
     <mergeCell ref="G8:X8"/>
     <mergeCell ref="Q20:S20"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/web/public/forms/chg-chongwal.xlsx
+++ b/web/public/forms/chg-chongwal.xlsx
@@ -596,7 +596,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
@@ -1521,7 +1521,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="M1" s="23" t="inlineStr">

--- a/web/public/forms/chg-chongwal.xlsx
+++ b/web/public/forms/chg-chongwal.xlsx
@@ -8,11 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="설계변경 총괄표" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'설계변경 총괄표'!$A$1:$X$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$X$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -130,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -195,9 +193,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -804,27 +799,18 @@
       <c r="H11" s="5" t="n"/>
       <c r="I11" s="5" t="n"/>
       <c r="J11" s="5" t="n"/>
-      <c r="K11" s="12">
-        <f>IF(N11="","",N(G7))</f>
-        <v/>
-      </c>
+      <c r="K11" s="12" t="n"/>
       <c r="L11" s="5" t="n"/>
       <c r="M11" s="5" t="n"/>
       <c r="N11" s="7" t="n"/>
       <c r="O11" s="5" t="n"/>
       <c r="P11" s="5" t="n"/>
-      <c r="Q11" s="12">
-        <f>IF(N11="","",K11+N11)</f>
-        <v/>
-      </c>
+      <c r="Q11" s="12" t="n"/>
       <c r="R11" s="5" t="n"/>
       <c r="S11" s="5" t="n"/>
       <c r="T11" s="13" t="n"/>
       <c r="U11" s="5" t="n"/>
-      <c r="V11" s="14">
-        <f>IF(AND(N11="",T11=""),"",G8+N(T11))</f>
-        <v/>
-      </c>
+      <c r="V11" s="14" t="n"/>
       <c r="W11" s="5" t="n"/>
       <c r="X11" s="5" t="n"/>
     </row>
@@ -839,27 +825,18 @@
       <c r="H12" s="5" t="n"/>
       <c r="I12" s="5" t="n"/>
       <c r="J12" s="5" t="n"/>
-      <c r="K12" s="12">
-        <f>IF(N12="","",N(G7)+SUM(N11:N11))</f>
-        <v/>
-      </c>
+      <c r="K12" s="12" t="n"/>
       <c r="L12" s="5" t="n"/>
       <c r="M12" s="5" t="n"/>
       <c r="N12" s="7" t="n"/>
       <c r="O12" s="5" t="n"/>
       <c r="P12" s="5" t="n"/>
-      <c r="Q12" s="12">
-        <f>IF(N12="","",K12+N12)</f>
-        <v/>
-      </c>
+      <c r="Q12" s="12" t="n"/>
       <c r="R12" s="5" t="n"/>
       <c r="S12" s="5" t="n"/>
       <c r="T12" s="13" t="n"/>
       <c r="U12" s="5" t="n"/>
-      <c r="V12" s="14">
-        <f>IF(AND(N12="",T12=""),"",G8+SUM(T11:T12))</f>
-        <v/>
-      </c>
+      <c r="V12" s="14" t="n"/>
       <c r="W12" s="5" t="n"/>
       <c r="X12" s="5" t="n"/>
     </row>
@@ -874,27 +851,18 @@
       <c r="H13" s="5" t="n"/>
       <c r="I13" s="5" t="n"/>
       <c r="J13" s="5" t="n"/>
-      <c r="K13" s="12">
-        <f>IF(N13="","",N(G7)+SUM(N11:N12))</f>
-        <v/>
-      </c>
+      <c r="K13" s="12" t="n"/>
       <c r="L13" s="5" t="n"/>
       <c r="M13" s="5" t="n"/>
       <c r="N13" s="7" t="n"/>
       <c r="O13" s="5" t="n"/>
       <c r="P13" s="5" t="n"/>
-      <c r="Q13" s="12">
-        <f>IF(N13="","",K13+N13)</f>
-        <v/>
-      </c>
+      <c r="Q13" s="12" t="n"/>
       <c r="R13" s="5" t="n"/>
       <c r="S13" s="5" t="n"/>
       <c r="T13" s="13" t="n"/>
       <c r="U13" s="5" t="n"/>
-      <c r="V13" s="14">
-        <f>IF(AND(N13="",T13=""),"",G8+SUM(T11:T13))</f>
-        <v/>
-      </c>
+      <c r="V13" s="14" t="n"/>
       <c r="W13" s="5" t="n"/>
       <c r="X13" s="5" t="n"/>
     </row>
@@ -909,27 +877,18 @@
       <c r="H14" s="5" t="n"/>
       <c r="I14" s="5" t="n"/>
       <c r="J14" s="5" t="n"/>
-      <c r="K14" s="12">
-        <f>IF(N14="","",N(G7)+SUM(N11:N13))</f>
-        <v/>
-      </c>
+      <c r="K14" s="12" t="n"/>
       <c r="L14" s="5" t="n"/>
       <c r="M14" s="5" t="n"/>
       <c r="N14" s="7" t="n"/>
       <c r="O14" s="5" t="n"/>
       <c r="P14" s="5" t="n"/>
-      <c r="Q14" s="12">
-        <f>IF(N14="","",K14+N14)</f>
-        <v/>
-      </c>
+      <c r="Q14" s="12" t="n"/>
       <c r="R14" s="5" t="n"/>
       <c r="S14" s="5" t="n"/>
       <c r="T14" s="13" t="n"/>
       <c r="U14" s="5" t="n"/>
-      <c r="V14" s="14">
-        <f>IF(AND(N14="",T14=""),"",G8+SUM(T11:T14))</f>
-        <v/>
-      </c>
+      <c r="V14" s="14" t="n"/>
       <c r="W14" s="5" t="n"/>
       <c r="X14" s="5" t="n"/>
     </row>
@@ -944,27 +903,18 @@
       <c r="H15" s="5" t="n"/>
       <c r="I15" s="5" t="n"/>
       <c r="J15" s="5" t="n"/>
-      <c r="K15" s="12">
-        <f>IF(N15="","",N(G7)+SUM(N11:N14))</f>
-        <v/>
-      </c>
+      <c r="K15" s="12" t="n"/>
       <c r="L15" s="5" t="n"/>
       <c r="M15" s="5" t="n"/>
       <c r="N15" s="7" t="n"/>
       <c r="O15" s="5" t="n"/>
       <c r="P15" s="5" t="n"/>
-      <c r="Q15" s="12">
-        <f>IF(N15="","",K15+N15)</f>
-        <v/>
-      </c>
+      <c r="Q15" s="12" t="n"/>
       <c r="R15" s="5" t="n"/>
       <c r="S15" s="5" t="n"/>
       <c r="T15" s="13" t="n"/>
       <c r="U15" s="5" t="n"/>
-      <c r="V15" s="14">
-        <f>IF(AND(N15="",T15=""),"",G8+SUM(T11:T15))</f>
-        <v/>
-      </c>
+      <c r="V15" s="14" t="n"/>
       <c r="W15" s="5" t="n"/>
       <c r="X15" s="5" t="n"/>
     </row>
@@ -979,27 +929,18 @@
       <c r="H16" s="5" t="n"/>
       <c r="I16" s="5" t="n"/>
       <c r="J16" s="5" t="n"/>
-      <c r="K16" s="12">
-        <f>IF(N16="","",N(G7)+SUM(N11:N15))</f>
-        <v/>
-      </c>
+      <c r="K16" s="12" t="n"/>
       <c r="L16" s="5" t="n"/>
       <c r="M16" s="5" t="n"/>
       <c r="N16" s="7" t="n"/>
       <c r="O16" s="5" t="n"/>
       <c r="P16" s="5" t="n"/>
-      <c r="Q16" s="12">
-        <f>IF(N16="","",K16+N16)</f>
-        <v/>
-      </c>
+      <c r="Q16" s="12" t="n"/>
       <c r="R16" s="5" t="n"/>
       <c r="S16" s="5" t="n"/>
       <c r="T16" s="13" t="n"/>
       <c r="U16" s="5" t="n"/>
-      <c r="V16" s="14">
-        <f>IF(AND(N16="",T16=""),"",G8+SUM(T11:T16))</f>
-        <v/>
-      </c>
+      <c r="V16" s="14" t="n"/>
       <c r="W16" s="5" t="n"/>
       <c r="X16" s="5" t="n"/>
     </row>
@@ -1014,27 +955,18 @@
       <c r="H17" s="5" t="n"/>
       <c r="I17" s="5" t="n"/>
       <c r="J17" s="5" t="n"/>
-      <c r="K17" s="12">
-        <f>IF(N17="","",N(G7)+SUM(N11:N16))</f>
-        <v/>
-      </c>
+      <c r="K17" s="12" t="n"/>
       <c r="L17" s="5" t="n"/>
       <c r="M17" s="5" t="n"/>
       <c r="N17" s="7" t="n"/>
       <c r="O17" s="5" t="n"/>
       <c r="P17" s="5" t="n"/>
-      <c r="Q17" s="12">
-        <f>IF(N17="","",K17+N17)</f>
-        <v/>
-      </c>
+      <c r="Q17" s="12" t="n"/>
       <c r="R17" s="5" t="n"/>
       <c r="S17" s="5" t="n"/>
       <c r="T17" s="13" t="n"/>
       <c r="U17" s="5" t="n"/>
-      <c r="V17" s="14">
-        <f>IF(AND(N17="",T17=""),"",G8+SUM(T11:T17))</f>
-        <v/>
-      </c>
+      <c r="V17" s="14" t="n"/>
       <c r="W17" s="5" t="n"/>
       <c r="X17" s="5" t="n"/>
     </row>
@@ -1049,27 +981,18 @@
       <c r="H18" s="5" t="n"/>
       <c r="I18" s="5" t="n"/>
       <c r="J18" s="5" t="n"/>
-      <c r="K18" s="12">
-        <f>IF(N18="","",N(G7)+SUM(N11:N17))</f>
-        <v/>
-      </c>
+      <c r="K18" s="12" t="n"/>
       <c r="L18" s="5" t="n"/>
       <c r="M18" s="5" t="n"/>
       <c r="N18" s="7" t="n"/>
       <c r="O18" s="5" t="n"/>
       <c r="P18" s="5" t="n"/>
-      <c r="Q18" s="12">
-        <f>IF(N18="","",K18+N18)</f>
-        <v/>
-      </c>
+      <c r="Q18" s="12" t="n"/>
       <c r="R18" s="5" t="n"/>
       <c r="S18" s="5" t="n"/>
       <c r="T18" s="13" t="n"/>
       <c r="U18" s="5" t="n"/>
-      <c r="V18" s="14">
-        <f>IF(AND(N18="",T18=""),"",G8+SUM(T11:T18))</f>
-        <v/>
-      </c>
+      <c r="V18" s="14" t="n"/>
       <c r="W18" s="5" t="n"/>
       <c r="X18" s="5" t="n"/>
     </row>
@@ -1084,27 +1007,18 @@
       <c r="H19" s="5" t="n"/>
       <c r="I19" s="5" t="n"/>
       <c r="J19" s="5" t="n"/>
-      <c r="K19" s="12">
-        <f>IF(N19="","",N(G7)+SUM(N11:N18))</f>
-        <v/>
-      </c>
+      <c r="K19" s="12" t="n"/>
       <c r="L19" s="5" t="n"/>
       <c r="M19" s="5" t="n"/>
       <c r="N19" s="7" t="n"/>
       <c r="O19" s="5" t="n"/>
       <c r="P19" s="5" t="n"/>
-      <c r="Q19" s="12">
-        <f>IF(N19="","",K19+N19)</f>
-        <v/>
-      </c>
+      <c r="Q19" s="12" t="n"/>
       <c r="R19" s="5" t="n"/>
       <c r="S19" s="5" t="n"/>
       <c r="T19" s="13" t="n"/>
       <c r="U19" s="5" t="n"/>
-      <c r="V19" s="14">
-        <f>IF(AND(N19="",T19=""),"",G8+SUM(T11:T19))</f>
-        <v/>
-      </c>
+      <c r="V19" s="14" t="n"/>
       <c r="W19" s="5" t="n"/>
       <c r="X19" s="5" t="n"/>
     </row>
@@ -1119,27 +1033,18 @@
       <c r="H20" s="5" t="n"/>
       <c r="I20" s="5" t="n"/>
       <c r="J20" s="5" t="n"/>
-      <c r="K20" s="12">
-        <f>IF(N20="","",N(G7)+SUM(N11:N19))</f>
-        <v/>
-      </c>
+      <c r="K20" s="12" t="n"/>
       <c r="L20" s="5" t="n"/>
       <c r="M20" s="5" t="n"/>
       <c r="N20" s="7" t="n"/>
       <c r="O20" s="5" t="n"/>
       <c r="P20" s="5" t="n"/>
-      <c r="Q20" s="12">
-        <f>IF(N20="","",K20+N20)</f>
-        <v/>
-      </c>
+      <c r="Q20" s="12" t="n"/>
       <c r="R20" s="5" t="n"/>
       <c r="S20" s="5" t="n"/>
       <c r="T20" s="13" t="n"/>
       <c r="U20" s="5" t="n"/>
-      <c r="V20" s="14">
-        <f>IF(AND(N20="",T20=""),"",G8+SUM(T11:T20))</f>
-        <v/>
-      </c>
+      <c r="V20" s="14" t="n"/>
       <c r="W20" s="5" t="n"/>
       <c r="X20" s="5" t="n"/>
     </row>
@@ -1163,10 +1068,7 @@
       <c r="D24" s="5" t="n"/>
       <c r="E24" s="5" t="n"/>
       <c r="F24" s="5" t="n"/>
-      <c r="G24" s="12">
-        <f>SUMIF(N11:N20,"&gt;0")</f>
-        <v/>
-      </c>
+      <c r="G24" s="12" t="n"/>
       <c r="H24" s="5" t="n"/>
       <c r="I24" s="5" t="n"/>
       <c r="J24" s="5" t="n"/>
@@ -1196,10 +1098,7 @@
       <c r="D25" s="5" t="n"/>
       <c r="E25" s="5" t="n"/>
       <c r="F25" s="5" t="n"/>
-      <c r="G25" s="12">
-        <f>SUMIF(N11:N20,"&lt;0")</f>
-        <v/>
-      </c>
+      <c r="G25" s="12" t="n"/>
       <c r="H25" s="5" t="n"/>
       <c r="I25" s="5" t="n"/>
       <c r="J25" s="5" t="n"/>
@@ -1229,10 +1128,7 @@
       <c r="D26" s="5" t="n"/>
       <c r="E26" s="5" t="n"/>
       <c r="F26" s="5" t="n"/>
-      <c r="G26" s="12">
-        <f>N(G7)+SUM(N11:N20)</f>
-        <v/>
-      </c>
+      <c r="G26" s="12" t="n"/>
       <c r="H26" s="5" t="n"/>
       <c r="I26" s="5" t="n"/>
       <c r="J26" s="5" t="n"/>
@@ -1262,10 +1158,7 @@
       <c r="D27" s="5" t="n"/>
       <c r="E27" s="5" t="n"/>
       <c r="F27" s="5" t="n"/>
-      <c r="G27" s="16">
-        <f>IF(N(G7)=0,"",SUM(N11:N20)/G7)</f>
-        <v/>
-      </c>
+      <c r="G27" s="16" t="n"/>
       <c r="H27" s="5" t="n"/>
       <c r="I27" s="5" t="n"/>
       <c r="J27" s="5" t="n"/>
@@ -1336,6 +1229,7 @@
       </c>
     </row>
     <row r="34" ht="6" customHeight="1"/>
+    <row r="35"/>
     <row r="36" ht="34" customHeight="1">
       <c r="A36" s="22" t="inlineStr">
         <is>
@@ -1480,985 +1374,4 @@
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:X36"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="3.6" customWidth="1" min="1" max="1"/>
-    <col width="3.6" customWidth="1" min="2" max="2"/>
-    <col width="3.6" customWidth="1" min="3" max="3"/>
-    <col width="3.6" customWidth="1" min="4" max="4"/>
-    <col width="3.6" customWidth="1" min="5" max="5"/>
-    <col width="3.6" customWidth="1" min="6" max="6"/>
-    <col width="3.6" customWidth="1" min="7" max="7"/>
-    <col width="3.6" customWidth="1" min="8" max="8"/>
-    <col width="3.6" customWidth="1" min="9" max="9"/>
-    <col width="3.6" customWidth="1" min="10" max="10"/>
-    <col width="3.6" customWidth="1" min="11" max="11"/>
-    <col width="3.6" customWidth="1" min="12" max="12"/>
-    <col width="3.6" customWidth="1" min="13" max="13"/>
-    <col width="3.6" customWidth="1" min="14" max="14"/>
-    <col width="3.6" customWidth="1" min="15" max="15"/>
-    <col width="3.6" customWidth="1" min="16" max="16"/>
-    <col width="3.6" customWidth="1" min="17" max="17"/>
-    <col width="3.6" customWidth="1" min="18" max="18"/>
-    <col width="3.6" customWidth="1" min="19" max="19"/>
-    <col width="3.6" customWidth="1" min="20" max="20"/>
-    <col width="3.6" customWidth="1" min="21" max="21"/>
-    <col width="3.6" customWidth="1" min="22" max="22"/>
-    <col width="3.6" customWidth="1" min="23" max="23"/>
-    <col width="3.6" customWidth="1" min="24" max="24"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="M1" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="6" customHeight="1"/>
-    <row r="3" ht="38" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>설 계 변 경 총 괄 표</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="10" customHeight="1"/>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  공 사 명</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>가나지구 배수로 정비공사</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="n"/>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
-      <c r="P5" s="5" t="n"/>
-      <c r="Q5" s="5" t="n"/>
-      <c r="R5" s="5" t="n"/>
-      <c r="S5" s="5" t="n"/>
-      <c r="T5" s="5" t="n"/>
-      <c r="U5" s="5" t="n"/>
-      <c r="V5" s="5" t="n"/>
-      <c r="W5" s="5" t="n"/>
-      <c r="X5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  계약번호</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>제2026-0312호</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-      <c r="P6" s="5" t="n"/>
-      <c r="Q6" s="5" t="n"/>
-      <c r="R6" s="5" t="n"/>
-      <c r="S6" s="5" t="n"/>
-      <c r="T6" s="5" t="n"/>
-      <c r="U6" s="5" t="n"/>
-      <c r="V6" s="5" t="n"/>
-      <c r="W6" s="5" t="n"/>
-      <c r="X6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  최초 계약금액</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="7" t="n">
-        <v>963241000</v>
-      </c>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
-      <c r="P7" s="5" t="n"/>
-      <c r="Q7" s="5" t="n"/>
-      <c r="R7" s="5" t="n"/>
-      <c r="S7" s="5" t="n"/>
-      <c r="T7" s="5" t="n"/>
-      <c r="U7" s="5" t="n"/>
-      <c r="V7" s="5" t="n"/>
-      <c r="W7" s="5" t="n"/>
-      <c r="X7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  최초 준공기한</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="8" t="n">
-        <v>46387</v>
-      </c>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-      <c r="P8" s="5" t="n"/>
-      <c r="Q8" s="5" t="n"/>
-      <c r="R8" s="5" t="n"/>
-      <c r="S8" s="5" t="n"/>
-      <c r="T8" s="5" t="n"/>
-      <c r="U8" s="5" t="n"/>
-      <c r="V8" s="5" t="n"/>
-      <c r="W8" s="5" t="n"/>
-      <c r="X8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="6" customHeight="1"/>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>차수</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>변경일자</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>사  유</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="9" t="inlineStr">
-        <is>
-          <t>변경 전 금액</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
-      <c r="N10" s="9" t="inlineStr">
-        <is>
-          <t>증감액</t>
-        </is>
-      </c>
-      <c r="O10" s="5" t="n"/>
-      <c r="P10" s="5" t="n"/>
-      <c r="Q10" s="9" t="inlineStr">
-        <is>
-          <t>변경 후 금액</t>
-        </is>
-      </c>
-      <c r="R10" s="5" t="n"/>
-      <c r="S10" s="5" t="n"/>
-      <c r="T10" s="9" t="inlineStr">
-        <is>
-          <t>공기증감(일)</t>
-        </is>
-      </c>
-      <c r="U10" s="5" t="n"/>
-      <c r="V10" s="9" t="inlineStr">
-        <is>
-          <t>변경 후 준공기한</t>
-        </is>
-      </c>
-      <c r="W10" s="5" t="n"/>
-      <c r="X10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>제1회</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="11" t="n">
-        <v>46188</v>
-      </c>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t>설계변경 — 배수관 연장 늘어남(실정보고 제3호)</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="12">
-        <f>IF(N11="","",N(G7))</f>
-        <v/>
-      </c>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="5" t="n"/>
-      <c r="N11" s="7" t="n">
-        <v>48650000</v>
-      </c>
-      <c r="O11" s="5" t="n"/>
-      <c r="P11" s="5" t="n"/>
-      <c r="Q11" s="12">
-        <f>IF(N11="","",K11+N11)</f>
-        <v/>
-      </c>
-      <c r="R11" s="5" t="n"/>
-      <c r="S11" s="5" t="n"/>
-      <c r="T11" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="U11" s="5" t="n"/>
-      <c r="V11" s="14">
-        <f>IF(AND(N11="",T11=""),"",G8+N(T11))</f>
-        <v/>
-      </c>
-      <c r="W11" s="5" t="n"/>
-      <c r="X11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>제2회</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="11" t="n">
-        <v>46254</v>
-      </c>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>물가변동 — 품목조정률 3.42%</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="12">
-        <f>IF(N12="","",N(G7)+SUM(N11:N11))</f>
-        <v/>
-      </c>
-      <c r="L12" s="5" t="n"/>
-      <c r="M12" s="5" t="n"/>
-      <c r="N12" s="7" t="n">
-        <v>21380000</v>
-      </c>
-      <c r="O12" s="5" t="n"/>
-      <c r="P12" s="5" t="n"/>
-      <c r="Q12" s="12">
-        <f>IF(N12="","",K12+N12)</f>
-        <v/>
-      </c>
-      <c r="R12" s="5" t="n"/>
-      <c r="S12" s="5" t="n"/>
-      <c r="T12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" s="5" t="n"/>
-      <c r="V12" s="14">
-        <f>IF(AND(N12="",T12=""),"",G8+SUM(T11:T12))</f>
-        <v/>
-      </c>
-      <c r="W12" s="5" t="n"/>
-      <c r="X12" s="5" t="n"/>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>제3회</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="11" t="n">
-        <v>46290</v>
-      </c>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>설계변경 — 포장 단면 조정(감)</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="12">
-        <f>IF(N13="","",N(G7)+SUM(N11:N12))</f>
-        <v/>
-      </c>
-      <c r="L13" s="5" t="n"/>
-      <c r="M13" s="5" t="n"/>
-      <c r="N13" s="7" t="n">
-        <v>-6120000</v>
-      </c>
-      <c r="O13" s="5" t="n"/>
-      <c r="P13" s="5" t="n"/>
-      <c r="Q13" s="12">
-        <f>IF(N13="","",K13+N13)</f>
-        <v/>
-      </c>
-      <c r="R13" s="5" t="n"/>
-      <c r="S13" s="5" t="n"/>
-      <c r="T13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" s="5" t="n"/>
-      <c r="V13" s="14">
-        <f>IF(AND(N13="",T13=""),"",G8+SUM(T11:T13))</f>
-        <v/>
-      </c>
-      <c r="W13" s="5" t="n"/>
-      <c r="X13" s="5" t="n"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="10" t="n"/>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="11" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="12">
-        <f>IF(N14="","",N(G7)+SUM(N11:N13))</f>
-        <v/>
-      </c>
-      <c r="L14" s="5" t="n"/>
-      <c r="M14" s="5" t="n"/>
-      <c r="N14" s="7" t="n"/>
-      <c r="O14" s="5" t="n"/>
-      <c r="P14" s="5" t="n"/>
-      <c r="Q14" s="12">
-        <f>IF(N14="","",K14+N14)</f>
-        <v/>
-      </c>
-      <c r="R14" s="5" t="n"/>
-      <c r="S14" s="5" t="n"/>
-      <c r="T14" s="13" t="n"/>
-      <c r="U14" s="5" t="n"/>
-      <c r="V14" s="14">
-        <f>IF(AND(N14="",T14=""),"",G8+SUM(T11:T14))</f>
-        <v/>
-      </c>
-      <c r="W14" s="5" t="n"/>
-      <c r="X14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="10" t="n"/>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="10" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="12">
-        <f>IF(N15="","",N(G7)+SUM(N11:N14))</f>
-        <v/>
-      </c>
-      <c r="L15" s="5" t="n"/>
-      <c r="M15" s="5" t="n"/>
-      <c r="N15" s="7" t="n"/>
-      <c r="O15" s="5" t="n"/>
-      <c r="P15" s="5" t="n"/>
-      <c r="Q15" s="12">
-        <f>IF(N15="","",K15+N15)</f>
-        <v/>
-      </c>
-      <c r="R15" s="5" t="n"/>
-      <c r="S15" s="5" t="n"/>
-      <c r="T15" s="13" t="n"/>
-      <c r="U15" s="5" t="n"/>
-      <c r="V15" s="14">
-        <f>IF(AND(N15="",T15=""),"",G8+SUM(T11:T15))</f>
-        <v/>
-      </c>
-      <c r="W15" s="5" t="n"/>
-      <c r="X15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="10" t="n"/>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="5" t="n"/>
-      <c r="K16" s="12">
-        <f>IF(N16="","",N(G7)+SUM(N11:N15))</f>
-        <v/>
-      </c>
-      <c r="L16" s="5" t="n"/>
-      <c r="M16" s="5" t="n"/>
-      <c r="N16" s="7" t="n"/>
-      <c r="O16" s="5" t="n"/>
-      <c r="P16" s="5" t="n"/>
-      <c r="Q16" s="12">
-        <f>IF(N16="","",K16+N16)</f>
-        <v/>
-      </c>
-      <c r="R16" s="5" t="n"/>
-      <c r="S16" s="5" t="n"/>
-      <c r="T16" s="13" t="n"/>
-      <c r="U16" s="5" t="n"/>
-      <c r="V16" s="14">
-        <f>IF(AND(N16="",T16=""),"",G8+SUM(T11:T16))</f>
-        <v/>
-      </c>
-      <c r="W16" s="5" t="n"/>
-      <c r="X16" s="5" t="n"/>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="10" t="n"/>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="11" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="10" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="12">
-        <f>IF(N17="","",N(G7)+SUM(N11:N16))</f>
-        <v/>
-      </c>
-      <c r="L17" s="5" t="n"/>
-      <c r="M17" s="5" t="n"/>
-      <c r="N17" s="7" t="n"/>
-      <c r="O17" s="5" t="n"/>
-      <c r="P17" s="5" t="n"/>
-      <c r="Q17" s="12">
-        <f>IF(N17="","",K17+N17)</f>
-        <v/>
-      </c>
-      <c r="R17" s="5" t="n"/>
-      <c r="S17" s="5" t="n"/>
-      <c r="T17" s="13" t="n"/>
-      <c r="U17" s="5" t="n"/>
-      <c r="V17" s="14">
-        <f>IF(AND(N17="",T17=""),"",G8+SUM(T11:T17))</f>
-        <v/>
-      </c>
-      <c r="W17" s="5" t="n"/>
-      <c r="X17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="10" t="n"/>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="11" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="12">
-        <f>IF(N18="","",N(G7)+SUM(N11:N17))</f>
-        <v/>
-      </c>
-      <c r="L18" s="5" t="n"/>
-      <c r="M18" s="5" t="n"/>
-      <c r="N18" s="7" t="n"/>
-      <c r="O18" s="5" t="n"/>
-      <c r="P18" s="5" t="n"/>
-      <c r="Q18" s="12">
-        <f>IF(N18="","",K18+N18)</f>
-        <v/>
-      </c>
-      <c r="R18" s="5" t="n"/>
-      <c r="S18" s="5" t="n"/>
-      <c r="T18" s="13" t="n"/>
-      <c r="U18" s="5" t="n"/>
-      <c r="V18" s="14">
-        <f>IF(AND(N18="",T18=""),"",G8+SUM(T11:T18))</f>
-        <v/>
-      </c>
-      <c r="W18" s="5" t="n"/>
-      <c r="X18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="10" t="n"/>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="11" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="10" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="12">
-        <f>IF(N19="","",N(G7)+SUM(N11:N18))</f>
-        <v/>
-      </c>
-      <c r="L19" s="5" t="n"/>
-      <c r="M19" s="5" t="n"/>
-      <c r="N19" s="7" t="n"/>
-      <c r="O19" s="5" t="n"/>
-      <c r="P19" s="5" t="n"/>
-      <c r="Q19" s="12">
-        <f>IF(N19="","",K19+N19)</f>
-        <v/>
-      </c>
-      <c r="R19" s="5" t="n"/>
-      <c r="S19" s="5" t="n"/>
-      <c r="T19" s="13" t="n"/>
-      <c r="U19" s="5" t="n"/>
-      <c r="V19" s="14">
-        <f>IF(AND(N19="",T19=""),"",G8+SUM(T11:T19))</f>
-        <v/>
-      </c>
-      <c r="W19" s="5" t="n"/>
-      <c r="X19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="10" t="n"/>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="11" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="10" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="12">
-        <f>IF(N20="","",N(G7)+SUM(N11:N19))</f>
-        <v/>
-      </c>
-      <c r="L20" s="5" t="n"/>
-      <c r="M20" s="5" t="n"/>
-      <c r="N20" s="7" t="n"/>
-      <c r="O20" s="5" t="n"/>
-      <c r="P20" s="5" t="n"/>
-      <c r="Q20" s="12">
-        <f>IF(N20="","",K20+N20)</f>
-        <v/>
-      </c>
-      <c r="R20" s="5" t="n"/>
-      <c r="S20" s="5" t="n"/>
-      <c r="T20" s="13" t="n"/>
-      <c r="U20" s="5" t="n"/>
-      <c r="V20" s="14">
-        <f>IF(AND(N20="",T20=""),"",G8+SUM(T11:T20))</f>
-        <v/>
-      </c>
-      <c r="W20" s="5" t="n"/>
-      <c r="X20" s="5" t="n"/>
-    </row>
-    <row r="21" ht="6" customHeight="1"/>
-    <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>※ 사유는 설계변경 / 물가변동 / 공기연장 으로 나누어 적습니다 — 근거 법령이 다릅니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="6" customHeight="1"/>
-    <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  증액 누계</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="12">
-        <f>SUMIF(N11:N20,"&gt;0")</f>
-        <v/>
-      </c>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="n"/>
-      <c r="L24" s="5" t="n"/>
-      <c r="M24" s="5" t="n"/>
-      <c r="N24" s="5" t="n"/>
-      <c r="O24" s="5" t="n"/>
-      <c r="P24" s="5" t="n"/>
-      <c r="Q24" s="5" t="n"/>
-      <c r="R24" s="5" t="n"/>
-      <c r="S24" s="5" t="n"/>
-      <c r="T24" s="5" t="n"/>
-      <c r="U24" s="5" t="n"/>
-      <c r="V24" s="5" t="n"/>
-      <c r="W24" s="5" t="n"/>
-      <c r="X24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  감액 누계</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="12">
-        <f>SUMIF(N11:N20,"&lt;0")</f>
-        <v/>
-      </c>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="5" t="n"/>
-      <c r="L25" s="5" t="n"/>
-      <c r="M25" s="5" t="n"/>
-      <c r="N25" s="5" t="n"/>
-      <c r="O25" s="5" t="n"/>
-      <c r="P25" s="5" t="n"/>
-      <c r="Q25" s="5" t="n"/>
-      <c r="R25" s="5" t="n"/>
-      <c r="S25" s="5" t="n"/>
-      <c r="T25" s="5" t="n"/>
-      <c r="U25" s="5" t="n"/>
-      <c r="V25" s="5" t="n"/>
-      <c r="W25" s="5" t="n"/>
-      <c r="X25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  현재 계약금액</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="12">
-        <f>N(G7)+SUM(N11:N20)</f>
-        <v/>
-      </c>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="n"/>
-      <c r="L26" s="5" t="n"/>
-      <c r="M26" s="5" t="n"/>
-      <c r="N26" s="5" t="n"/>
-      <c r="O26" s="5" t="n"/>
-      <c r="P26" s="5" t="n"/>
-      <c r="Q26" s="5" t="n"/>
-      <c r="R26" s="5" t="n"/>
-      <c r="S26" s="5" t="n"/>
-      <c r="T26" s="5" t="n"/>
-      <c r="U26" s="5" t="n"/>
-      <c r="V26" s="5" t="n"/>
-      <c r="W26" s="5" t="n"/>
-      <c r="X26" s="5" t="n"/>
-    </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  최초 대비 증감률</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="16">
-        <f>IF(N(G7)=0,"",SUM(N11:N20)/G7)</f>
-        <v/>
-      </c>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="5" t="n"/>
-      <c r="L27" s="5" t="n"/>
-      <c r="M27" s="5" t="n"/>
-      <c r="N27" s="5" t="n"/>
-      <c r="O27" s="5" t="n"/>
-      <c r="P27" s="5" t="n"/>
-      <c r="Q27" s="5" t="n"/>
-      <c r="R27" s="5" t="n"/>
-      <c r="S27" s="5" t="n"/>
-      <c r="T27" s="5" t="n"/>
-      <c r="U27" s="5" t="n"/>
-      <c r="V27" s="5" t="n"/>
-      <c r="W27" s="5" t="n"/>
-      <c r="X27" s="5" t="n"/>
-    </row>
-    <row r="28" ht="6" customHeight="1"/>
-    <row r="29" ht="10" customHeight="1"/>
-    <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="17" t="n">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="18" t="inlineStr"/>
-      <c r="K31" s="19" t="inlineStr">
-        <is>
-          <t>현장대리인</t>
-        </is>
-      </c>
-      <c r="Q31" s="20" t="inlineStr">
-        <is>
-          <t>김철수</t>
-        </is>
-      </c>
-      <c r="U31" s="21" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="18" t="inlineStr"/>
-      <c r="K32" s="19" t="inlineStr">
-        <is>
-          <t>감독</t>
-        </is>
-      </c>
-      <c r="Q32" s="20" t="inlineStr">
-        <is>
-          <t>박감독</t>
-        </is>
-      </c>
-      <c r="U32" s="21" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="18" t="inlineStr"/>
-      <c r="K33" s="19" t="inlineStr">
-        <is>
-          <t>발주기관</t>
-        </is>
-      </c>
-      <c r="Q33" s="20" t="inlineStr">
-        <is>
-          <t>건설과장</t>
-        </is>
-      </c>
-      <c r="U33" s="21" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="6" customHeight="1"/>
-    <row r="36" ht="19.5" customHeight="1">
-      <c r="A36" s="22" t="inlineStr">
-        <is>
-          <t>이 시트는 작성 예시입니다(가상의 현장 · 이름 · 금액). 실제로는 앞 시트에 적으세요.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="122">
-    <mergeCell ref="V10:X10"/>
-    <mergeCell ref="Q14:S14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="F10:J10"/>
-    <mergeCell ref="F19:J19"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="K31:P31"/>
-    <mergeCell ref="A3:X3"/>
-    <mergeCell ref="Q15:S15"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="U31:X31"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="F18:J18"/>
-    <mergeCell ref="K17:M17"/>
-    <mergeCell ref="F17:J17"/>
-    <mergeCell ref="T12:U12"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="V12:X12"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="K33:P33"/>
-    <mergeCell ref="V14:X14"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="V13:X13"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A32:J32"/>
-    <mergeCell ref="G7:X7"/>
-    <mergeCell ref="Q19:S19"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="T10:U10"/>
-    <mergeCell ref="G24:X24"/>
-    <mergeCell ref="A31:J31"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="A25:F25"/>
-    <mergeCell ref="G26:X26"/>
-    <mergeCell ref="A22:X22"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="T11:U11"/>
-    <mergeCell ref="G25:X25"/>
-    <mergeCell ref="Q13:S13"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="V17:X17"/>
-    <mergeCell ref="Q16:S16"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="U32:X32"/>
-    <mergeCell ref="A30:X30"/>
-    <mergeCell ref="Q31:T31"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="Q18:S18"/>
-    <mergeCell ref="V20:X20"/>
-    <mergeCell ref="F14:J14"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="U33:X33"/>
-    <mergeCell ref="F11:J11"/>
-    <mergeCell ref="T15:U15"/>
-    <mergeCell ref="Q10:S10"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="V15:X15"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="F15:J15"/>
-    <mergeCell ref="F12:J12"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="Q17:S17"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="V16:X16"/>
-    <mergeCell ref="K13:M13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="V18:X18"/>
-    <mergeCell ref="T17:U17"/>
-    <mergeCell ref="Q12:S12"/>
-    <mergeCell ref="K15:M15"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="T19:U19"/>
-    <mergeCell ref="G27:X27"/>
-    <mergeCell ref="A33:J33"/>
-    <mergeCell ref="V19:X19"/>
-    <mergeCell ref="K32:P32"/>
-    <mergeCell ref="F16:J16"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="T14:U14"/>
-    <mergeCell ref="G6:X6"/>
-    <mergeCell ref="Q32:T32"/>
-    <mergeCell ref="V11:X11"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="F20:J20"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="G5:X5"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="Q11:S11"/>
-    <mergeCell ref="Q33:T33"/>
-    <mergeCell ref="K19:M19"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="T13:U13"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="T16:U16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="M1:X1"/>
-    <mergeCell ref="T18:U18"/>
-    <mergeCell ref="A36:X36"/>
-    <mergeCell ref="G8:X8"/>
-    <mergeCell ref="Q20:S20"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/web/public/forms/chg-chongwal.xlsx
+++ b/web/public/forms/chg-chongwal.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
